--- a/premise/data/additional_inventories/lci-home-batteries.xlsx
+++ b/premise/data/additional_inventories/lci-home-batteries.xlsx
@@ -913,7 +913,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L212"/>
+  <dimension ref="A1:L250"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.5" customWidth="1"/>
@@ -1546,8 +1546,20 @@
       <c r="A34" t="s">
         <v>7</v>
       </c>
-      <c r="B34" t="s">
-        <v>127</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>APPROVED HOME-STORAGE CELL/CAPACITY RECONCILIATION, issue65,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells. Retain labelled14.4kWhLFP and19.5kWhNMC811 grossnominalcapacity. Previous161.28kgmodule*0.63=101.6064kgcells produces14.224896/19.305216kWh even at copied140/190Wh/kg,and the actually linkedgenericcell reference is different again. Adopt the already accepted chemistry-specific160/280Wh/kg reference,so manufacture90kgLFPcells or69.642857142857kgNMC811cells per installedhome system. This selects a coherent currentcell-reference variant; it is NOT evidence original sourcecapacity or measuredcellmass were wrong. Source-specific Mohr cell inventories and precise pouch geometry remain a comparison gap. Preserve54.8352kgmodule steel,4.8384kg moduleBMS and their existingmanufacturing/transport proxies as fixed engineeringhousing architecture; do not fill releasedcellmass with arbitrarymetal tohold161.28kg. New moduleprovider is oneunit for allinstalledmodules in onehome system,not onekg or onephysicalcell. Retain exactcell supplier/product/location from corrected chemistry hardware provider; nocompletepack or extra centralBMS input. Update freight pernewmodulemanufacturedmass using existingonekg-route intensities,while currentnoncell hardware references remainfixed. Cell manufacture energy is includedupstream,not chargedagain. Original288kgsourcewholeHSS mass and140/190Wh/kgmetadata are historical,not the updatedengineeringvariant; complete noncell component retainedmass/yields are not certified by newmodule closure. ModulebaselineLFP149.6736kg,NMC129.316457142857kg excludesother unchangedHSSperiphery. No source systemlifetime,operatingloss,DoD orreplacement change here; issues66/67 reconcilethose separately. This fixedhomecell-design path does not silently inheritmobile futuredensitylearning. Existing legacykgmoduleprovidersremainavailable forother consumers. No native/runtime edits or recyclingcredits; omitteddevice-specificEOL remains explicitgap. Currentreference:chemistryLFP,nominal14.4kWh,cell specific energy160.0Wh/kg,installedcellmass90.0kg,modulenoncellmass59.6736kg,totalmodulemass149.6736kg.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Life cycle assessment (LCA) of a battery home storage system based on primary data, Friedrich B. Jasper, Jana Spathe, Manuel Baumann, Jens F. Peters, Janna Ruhland, Marcel Weil, 2020, Journal of Cleaner Production
+Cell type: LFP, Energy density in Wh/kg:140, Cycle lifetime: 2500-10000, Calendar lifetime in years:13-20, Efficiency in %: 93, Development stage: Mature, Storage Capacity of the HSS in kWh:14.4. Weight: 288 kg.
+Variable	LFP	LFP	SIB	NMC811	NMC811
+Energy Density (Wh/kg)	140	140	128	190	200
+Resulting Capacity (kWh)	14.4	14.4	13.1657	19.5429	20.5714
+Round Trip efficiency system	0.815	0.815	0.815	0.815	0.815
+Depth of discharge	0.9	0.9	0.8	0.8	0.8
+electricity standby consumption (W)	22.5	22.5	22.5	22.5	22.5
+Time of standby per year (h)	6000	6000	6000	6000	6000</t>
+        </is>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -1741,20 +1753,28 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>112</v>
-      </c>
-      <c r="B44" t="s">
-        <v>113</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cell modules, home 14.4kWh LFP, capacity-consistent reference</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>cell modules, home 14.4kWh LFP, capacity-consistent reference</t>
+        </is>
       </c>
       <c r="C44">
-        <v>161.28000000000003</v>
-      </c>
-      <c r="D44" t="s">
-        <v>76</v>
-      </c>
-      <c r="E44" t="s">
-        <v>16</v>
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
       </c>
       <c r="F44" t="s">
         <v>89</v>
@@ -1853,8 +1873,20 @@
       <c r="A53" t="s">
         <v>7</v>
       </c>
-      <c r="B53" t="s">
-        <v>127</v>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>APPROVED HOME-STORAGE CELL/CAPACITY RECONCILIATION, issue65,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells. Retain labelled14.4kWhLFP and19.5kWhNMC811 grossnominalcapacity. Previous161.28kgmodule*0.63=101.6064kgcells produces14.224896/19.305216kWh even at copied140/190Wh/kg,and the actually linkedgenericcell reference is different again. Adopt the already accepted chemistry-specific160/280Wh/kg reference,so manufacture90kgLFPcells or69.642857142857kgNMC811cells per installedhome system. This selects a coherent currentcell-reference variant; it is NOT evidence original sourcecapacity or measuredcellmass were wrong. Source-specific Mohr cell inventories and precise pouch geometry remain a comparison gap. Preserve54.8352kgmodule steel,4.8384kg moduleBMS and their existingmanufacturing/transport proxies as fixed engineeringhousing architecture; do not fill releasedcellmass with arbitrarymetal tohold161.28kg. New moduleprovider is oneunit for allinstalledmodules in onehome system,not onekg or onephysicalcell. Retain exactcell supplier/product/location from corrected chemistry hardware provider; nocompletepack or extra centralBMS input. Update freight pernewmodulemanufacturedmass using existingonekg-route intensities,while currentnoncell hardware references remainfixed. Cell manufacture energy is includedupstream,not chargedagain. Original288kgsourcewholeHSS mass and140/190Wh/kgmetadata are historical,not the updatedengineeringvariant; complete noncell component retainedmass/yields are not certified by newmodule closure. ModulebaselineLFP149.6736kg,NMC129.316457142857kg excludesother unchangedHSSperiphery. No source systemlifetime,operatingloss,DoD orreplacement change here; issues66/67 reconcilethose separately. This fixedhomecell-design path does not silently inheritmobile futuredensitylearning. Existing legacykgmoduleprovidersremainavailable forother consumers. No native/runtime edits or recyclingcredits; omitteddevice-specificEOL remains explicitgap. Currentreference:chemistryNMC811,nominal19.5kWh,cell specific energy280.0Wh/kg,installedcellmass69.64285714285714kg,modulenoncellmass59.6736kg,totalmodulemass129.31645714285713kg.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Life cycle assessment (LCA) of a battery home storage system based on primary data, Friedrich B. Jasper, Jana Spathe, Manuel Baumann, Jens F. Peters, Janna Ruhland, Marcel Weil, 2020, Journal of Cleaner Production
+Cell type: LFP, Energy density in Wh/kg:140, Cycle lifetime: 2500-10000, Calendar lifetime in years:13-20, Efficiency in %: 93, Development stage: Mature, Storage Capacity of the HSS in kWh:14.4. Weight: 288 kg.
+Variable	LFP	LFP	SIB	NMC811	NMC811
+Energy Density (Wh/kg)	140	140	128	190	200
+Resulting Capacity (kWh)	14.4	14.4	13.1657	19.5429	20.5714
+Round Trip efficiency system	0.815	0.815	0.815	0.815	0.815
+Depth of discharge	0.9	0.9	0.8	0.8	0.8
+electricity standby consumption (W)	22.5	22.5	22.5	22.5	22.5
+Time of standby per year (h)	6000	6000	6000	6000	6000</t>
+        </is>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
@@ -2048,20 +2080,28 @@
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>128</v>
-      </c>
-      <c r="B63" t="s">
-        <v>129</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cell modules, home 19.5kWh NMC811, capacity-consistent reference</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>cell modules, home 19.5kWh NMC811, capacity-consistent reference</t>
+        </is>
       </c>
       <c r="C63">
-        <v>161.28000000000003</v>
-      </c>
-      <c r="D63" t="s">
-        <v>76</v>
-      </c>
-      <c r="E63" t="s">
-        <v>16</v>
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
       </c>
       <c r="F63" t="s">
         <v>89</v>
@@ -4454,6 +4494,838 @@
         <v>74</v>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>cell modules, home 14.4kWh LFP, capacity-consistent reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>cell modules, home 14.4kWh LFP, capacity-consistent reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>APPROVED HOME-STORAGE CELL/CAPACITY RECONCILIATION, issue65,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells. Retain labelled14.4kWhLFP and19.5kWhNMC811 grossnominalcapacity. Previous161.28kgmodule*0.63=101.6064kgcells produces14.224896/19.305216kWh even at copied140/190Wh/kg,and the actually linkedgenericcell reference is different again. Adopt the already accepted chemistry-specific160/280Wh/kg reference,so manufacture90kgLFPcells or69.642857142857kgNMC811cells per installedhome system. This selects a coherent currentcell-reference variant; it is NOT evidence original sourcecapacity or measuredcellmass were wrong. Source-specific Mohr cell inventories and precise pouch geometry remain a comparison gap. Preserve54.8352kgmodule steel,4.8384kg moduleBMS and their existingmanufacturing/transport proxies as fixed engineeringhousing architecture; do not fill releasedcellmass with arbitrarymetal tohold161.28kg. New moduleprovider is oneunit for allinstalledmodules in onehome system,not onekg or onephysicalcell. Retain exactcell supplier/product/location from corrected chemistry hardware provider; nocompletepack or extra centralBMS input. Update freight pernewmodulemanufacturedmass using existingonekg-route intensities,while currentnoncell hardware references remainfixed. Cell manufacture energy is includedupstream,not chargedagain. Original288kgsourcewholeHSS mass and140/190Wh/kgmetadata are historical,not the updatedengineeringvariant; complete noncell component retainedmass/yields are not certified by newmodule closure. ModulebaselineLFP149.6736kg,NMC129.316457142857kg excludesother unchangedHSSperiphery. No source systemlifetime,operatingloss,DoD orreplacement change here; issues66/67 reconcilethose separately. This fixedhomecell-design path does not silently inheritmobile futuredensitylearning. Existing legacykgmoduleprovidersremainavailable forother consumers. No native/runtime edits or recyclingcredits; omitteddevice-specificEOL remains explicitgap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>cell modules, home 14.4kWh LFP, capacity-consistent reference</t>
+        </is>
+      </c>
+      <c r="B224">
+        <v>1</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>cell modules, home 14.4kWh LFP, capacity-consistent reference</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>cell modules, home 14.4kWh LFP, capacity-consistent reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>battery module system production</t>
+        </is>
+      </c>
+      <c r="B225">
+        <v>4.8384</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>battery module system for home storage system module</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>battery module system for home storage system module</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>market for battery cell, Li-ion, LFP</t>
+        </is>
+      </c>
+      <c r="B226">
+        <v>90.0</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, LFP</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, LFP</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>market for metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B227">
+        <v>54.83520000000001</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B228">
+        <v>54.83520000000001</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>market for transport, freight train</t>
+        </is>
+      </c>
+      <c r="B229">
+        <v>149.6736</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>market for transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+      <c r="B230">
+        <v>149.6736</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>market for transport, freight, sea, container ship</t>
+        </is>
+      </c>
+      <c r="B231">
+        <v>1197.3888</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>transport, freight, sea, container ship</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>transport, freight, sea, container ship</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>cell modules, home 19.5kWh NMC811, capacity-consistent reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>cell modules, home 19.5kWh NMC811, capacity-consistent reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>APPROVED HOME-STORAGE CELL/CAPACITY RECONCILIATION, issue65,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells. Retain labelled14.4kWhLFP and19.5kWhNMC811 grossnominalcapacity. Previous161.28kgmodule*0.63=101.6064kgcells produces14.224896/19.305216kWh even at copied140/190Wh/kg,and the actually linkedgenericcell reference is different again. Adopt the already accepted chemistry-specific160/280Wh/kg reference,so manufacture90kgLFPcells or69.642857142857kgNMC811cells per installedhome system. This selects a coherent currentcell-reference variant; it is NOT evidence original sourcecapacity or measuredcellmass were wrong. Source-specific Mohr cell inventories and precise pouch geometry remain a comparison gap. Preserve54.8352kgmodule steel,4.8384kg moduleBMS and their existingmanufacturing/transport proxies as fixed engineeringhousing architecture; do not fill releasedcellmass with arbitrarymetal tohold161.28kg. New moduleprovider is oneunit for allinstalledmodules in onehome system,not onekg or onephysicalcell. Retain exactcell supplier/product/location from corrected chemistry hardware provider; nocompletepack or extra centralBMS input. Update freight pernewmodulemanufacturedmass using existingonekg-route intensities,while currentnoncell hardware references remainfixed. Cell manufacture energy is includedupstream,not chargedagain. Original288kgsourcewholeHSS mass and140/190Wh/kgmetadata are historical,not the updatedengineeringvariant; complete noncell component retainedmass/yields are not certified by newmodule closure. ModulebaselineLFP149.6736kg,NMC129.316457142857kg excludesother unchangedHSSperiphery. No source systemlifetime,operatingloss,DoD orreplacement change here; issues66/67 reconcilethose separately. This fixedhomecell-design path does not silently inheritmobile futuredensitylearning. Existing legacykgmoduleprovidersremainavailable forother consumers. No native/runtime edits or recyclingcredits; omitteddevice-specificEOL remains explicitgap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>cell modules, home 19.5kWh NMC811, capacity-consistent reference</t>
+        </is>
+      </c>
+      <c r="B243">
+        <v>1</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>cell modules, home 19.5kWh NMC811, capacity-consistent reference</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>cell modules, home 19.5kWh NMC811, capacity-consistent reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>battery module system production</t>
+        </is>
+      </c>
+      <c r="B244">
+        <v>4.8384</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>battery module system for home storage system module</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>battery module system for home storage system module</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+        </is>
+      </c>
+      <c r="B245">
+        <v>69.64285714285714</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>market for metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B246">
+        <v>54.83520000000001</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B247">
+        <v>54.83520000000001</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>market for transport, freight train</t>
+        </is>
+      </c>
+      <c r="B248">
+        <v>129.31645714285713</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>market for transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+      <c r="B249">
+        <v>129.31645714285713</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>market for transport, freight, sea, container ship</t>
+        </is>
+      </c>
+      <c r="B250">
+        <v>1034.531657142857</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>transport, freight, sea, container ship</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>transport, freight, sea, container ship</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/premise/data/additional_inventories/lci-home-batteries.xlsx
+++ b/premise/data/additional_inventories/lci-home-batteries.xlsx
@@ -966,8 +966,12 @@
       <c r="A5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>139</v>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>APPROVED HOME-STORAGE DELIVERED-ENERGY BOUNDARY, issue66,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899 section2.4,pages5-6 andTable2. Source0.815charge/discharge efficiency explicitly excludesstandby. Standby22.5W for6000h/year,halffromchargedbattery andhalffromgrid. Retain existing modeled13year/2500cycle scenario rather than silently adopting paper20year/7300cycle reference. Sourcepaper section2.2 specifies maximum80%LFPDoD,contradicting the copiedworkbook90%table. Choose0.8DoDforbothchemistries; NMCretains its existing0.8engineeringreference at existing14.4/19.5nominalkWh. Consumer-deliveredlifetimeenergyQ=capacity*DoD*2500cycles:28800kWhLFP,39000kWhNMC811. Retain13yearcalendar horizon and2500operatingcycles; this is a documentedmodelscenario,not manufacturer measuredlife or automaticonecycleperday. StandbyS=.0225kW*6000h/year*13years=1755kWh. Chargepurchase=(Q+S/2)/0.815; directgridstandby=S/2. Per1kWhconsumeroutput,firstinput=(1+S/(2Q))/0.815 andsecond=S/(2Q),so battery-suppliedstandby ischargedandlost once.0.815alreadyincludescycleconversionlosses,notstandby; do not multiply again by cell93%efficiency or add19%instead of dividingbyefficiency. Existingtwoelectricitysupplier identities retained as a grid-referencecase:thepaperhalfPV/halfgrid assumption is not a newSwisshourlychargingmix. No newPVcapacity oralteredselfconsumptionprofile. System manufacture dose=1/Q,firstwholeinstalledset; componentreplacements handledseparately byissue67 withoutanotherlifetime divisor. CorrectLFPcopiedNMCcomment and2020citationto2022. Capacity isgross; DoD already limitsusableenergy,do not reapplyit in cell manufacture. Uncertainty of actualcycleefficiency,standbyhours,loadsanddegradation remain explicit; sourcepaper itselfuses literatureusephasevalues. No premature newprimarysecondary orrecoverycredit. Staticnominalcapacity andno degradationreference imply constantcycleoutput; futureagingprofile needs a separate sourceddesign. Actualscenario:19.5kWh gross,0.8DoD,Q=39000.0kWh,S=1755.0kWh,chargeinput=1.2546012269938651kWh/outputkWh,directstandby=0.0225kWh/outputkWh.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+1 kWh of electricity discharged from a stationary battery. Accounts for charge and discharge losses: 19%. The original dataset is a 19.5 kWh home storage system, using NMC811 cells. The system has a stand-by consumption of 22 W over 6000 hours per year. Assumes lifetime of 2500 charge-discharge cycles over 13 years, and a maximum depth of discharge of 80%. In total, the system delivers 2500 [cycles] x 80% x 19.5 [Wh] = 39000 kWh.</t>
+        </is>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -1109,8 +1113,8 @@
         <v>135</v>
       </c>
       <c r="B12" s="17">
-        <f>1*1.19</f>
-        <v>1.19</v>
+        <f>1.2546012269938651</f>
+        <v>1.2546012269938651</v>
       </c>
       <c r="C12" t="s">
         <v>140</v>
@@ -1132,16 +1136,16 @@
         <v>5</v>
       </c>
       <c r="J12" s="17">
-        <f>B12</f>
-        <v>1.19</v>
+        <f>1.2546012269938651</f>
+        <v>1.2546012269938651</v>
       </c>
       <c r="K12">
-        <f>1*1.1</f>
-        <v>1.1000000000000001</v>
+        <f>1.1597154199102955</f>
+        <v>1.1597154199102955</v>
       </c>
       <c r="L12">
-        <f>1*1.25</f>
-        <v>1.25</v>
+        <f>1.3178584317162447</f>
+        <v>1.3178584317162447</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -1149,8 +1153,8 @@
         <v>135</v>
       </c>
       <c r="B13" s="17">
-        <f>((22/1000)*6000*13)/(2500*19.5*0.8)</f>
-        <v>4.3999999999999997E-2</v>
+        <f>0.0225</f>
+        <v>0.0225</v>
       </c>
       <c r="C13" t="s">
         <v>140</v>
@@ -1175,8 +1179,8 @@
         <v>130</v>
       </c>
       <c r="B14" s="17">
-        <f>1/(2500*80%*19.5)</f>
-        <v>2.564102564102564E-5</v>
+        <f>2.564102564102564e-05</f>
+        <v>2.564102564102564e-05</v>
       </c>
       <c r="C14" t="s">
         <v>16</v>
@@ -1198,16 +1202,16 @@
         <v>5</v>
       </c>
       <c r="J14" s="17">
-        <f>B14</f>
-        <v>2.564102564102564E-5</v>
+        <f>2.564102564102564e-05</f>
+        <v>2.564102564102564e-05</v>
       </c>
       <c r="K14">
-        <f>1/(3000*80%*19.5)</f>
-        <v>2.1367521367521368E-5</v>
+        <f>2.1367521367521368e-05</f>
+        <v>2.1367521367521368e-05</v>
       </c>
       <c r="L14">
-        <f>1/(2000*80%*19.5)</f>
-        <v>3.2051282051282051E-5</v>
+        <f>3.205128205128205e-05</f>
+        <v>3.205128205128205e-05</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -1252,8 +1256,12 @@
       <c r="A18" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>139</v>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>APPROVED HOME-STORAGE DELIVERED-ENERGY BOUNDARY, issue66,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899 section2.4,pages5-6 andTable2. Source0.815charge/discharge efficiency explicitly excludesstandby. Standby22.5W for6000h/year,halffromchargedbattery andhalffromgrid. Retain existing modeled13year/2500cycle scenario rather than silently adopting paper20year/7300cycle reference. Sourcepaper section2.2 specifies maximum80%LFPDoD,contradicting the copiedworkbook90%table. Choose0.8DoDforbothchemistries; NMCretains its existing0.8engineeringreference at existing14.4/19.5nominalkWh. Consumer-deliveredlifetimeenergyQ=capacity*DoD*2500cycles:28800kWhLFP,39000kWhNMC811. Retain13yearcalendar horizon and2500operatingcycles; this is a documentedmodelscenario,not manufacturer measuredlife or automaticonecycleperday. StandbyS=.0225kW*6000h/year*13years=1755kWh. Chargepurchase=(Q+S/2)/0.815; directgridstandby=S/2. Per1kWhconsumeroutput,firstinput=(1+S/(2Q))/0.815 andsecond=S/(2Q),so battery-suppliedstandby ischargedandlost once.0.815alreadyincludescycleconversionlosses,notstandby; do not multiply again by cell93%efficiency or add19%instead of dividingbyefficiency. Existingtwoelectricitysupplier identities retained as a grid-referencecase:thepaperhalfPV/halfgrid assumption is not a newSwisshourlychargingmix. No newPVcapacity oralteredselfconsumptionprofile. System manufacture dose=1/Q,firstwholeinstalledset; componentreplacements handledseparately byissue67 withoutanotherlifetime divisor. CorrectLFPcopiedNMCcomment and2020citationto2022. Capacity isgross; DoD already limitsusableenergy,do not reapplyit in cell manufacture. Uncertainty of actualcycleefficiency,standbyhours,loadsanddegradation remain explicit; sourcepaper itselfuses literatureusephasevalues. No premature newprimarysecondary orrecoverycredit. Staticnominalcapacity andno degradationreference imply constantcycleoutput; futureagingprofile needs a separate sourceddesign. Actualscenario:14.4kWh gross,0.8DoD,Q=28800.000000000004kWh,S=1755.0kWh,chargeinput=1.2643788343558284kWh/outputkWh,directstandby=0.030468749999999996kWh/outputkWh.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+1 kWh of electricity discharged from a stationary battery. Accounts for charge and discharge losses: 19%. The original dataset is a 19.5 kWh home storage system, using NMC811 cells. The system has a stand-by consumption of 22 W over 6000 hours per year. Assumes lifetime of 2500 charge-discharge cycles over 13 years, and a maximum depth of discharge of 80%. In total, the system delivers 2500 [cycles] x 80% x 19.5 [Wh] = 39000 kWh.</t>
+        </is>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -1395,8 +1403,8 @@
         <v>135</v>
       </c>
       <c r="B25" s="17">
-        <f>1*1.19</f>
-        <v>1.19</v>
+        <f>1.2643788343558284</f>
+        <v>1.2643788343558284</v>
       </c>
       <c r="C25" t="s">
         <v>140</v>
@@ -1418,16 +1426,16 @@
         <v>5</v>
       </c>
       <c r="J25" s="17">
-        <f>B25</f>
-        <v>1.19</v>
+        <f>1.2643788343558284</f>
+        <v>1.2643788343558284</v>
       </c>
       <c r="K25">
-        <f>1*1.1</f>
-        <v>1.1000000000000001</v>
+        <f>1.1687535443625308</f>
+        <v>1.1687535443625308</v>
       </c>
       <c r="L25">
-        <f>1*1.25</f>
-        <v>1.25</v>
+        <f>1.3281290276846938</f>
+        <v>1.3281290276846938</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
@@ -1435,8 +1443,8 @@
         <v>135</v>
       </c>
       <c r="B26" s="17">
-        <f>((22/1000)*6000*13)/(2500*19.5*0.8)</f>
-        <v>4.3999999999999997E-2</v>
+        <f>0.030468749999999996</f>
+        <v>0.030468749999999996</v>
       </c>
       <c r="C26" t="s">
         <v>140</v>
@@ -1461,8 +1469,8 @@
         <v>123</v>
       </c>
       <c r="B27" s="17">
-        <f>1/(2500*80%*14.4)</f>
-        <v>3.4722222222222222E-5</v>
+        <f>3.4722222222222215e-05</f>
+        <v>3.4722222222222215e-05</v>
       </c>
       <c r="C27" t="s">
         <v>16</v>
@@ -1484,16 +1492,16 @@
         <v>5</v>
       </c>
       <c r="J27" s="17">
-        <f>B27</f>
-        <v>3.4722222222222222E-5</v>
+        <f>3.4722222222222215e-05</f>
+        <v>3.4722222222222215e-05</v>
       </c>
       <c r="K27">
-        <f>1/(3000*80%*14.4)</f>
-        <v>2.8935185185185186E-5</v>
+        <f>2.8935185185185183e-05</f>
+        <v>2.8935185185185183e-05</v>
       </c>
       <c r="L27">
-        <f>1/(2000*80%*14.4)</f>
-        <v>4.3402777777777779E-5</v>
+        <f>4.340277777777777e-05</f>
+        <v>4.340277777777777e-05</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-home-batteries.xlsx
+++ b/premise/data/additional_inventories/lci-home-batteries.xlsx
@@ -1556,7 +1556,9 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>APPROVED HOME-STORAGE CELL/CAPACITY RECONCILIATION, issue65,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells. Retain labelled14.4kWhLFP and19.5kWhNMC811 grossnominalcapacity. Previous161.28kgmodule*0.63=101.6064kgcells produces14.224896/19.305216kWh even at copied140/190Wh/kg,and the actually linkedgenericcell reference is different again. Adopt the already accepted chemistry-specific160/280Wh/kg reference,so manufacture90kgLFPcells or69.642857142857kgNMC811cells per installedhome system. This selects a coherent currentcell-reference variant; it is NOT evidence original sourcecapacity or measuredcellmass were wrong. Source-specific Mohr cell inventories and precise pouch geometry remain a comparison gap. Preserve54.8352kgmodule steel,4.8384kg moduleBMS and their existingmanufacturing/transport proxies as fixed engineeringhousing architecture; do not fill releasedcellmass with arbitrarymetal tohold161.28kg. New moduleprovider is oneunit for allinstalledmodules in onehome system,not onekg or onephysicalcell. Retain exactcell supplier/product/location from corrected chemistry hardware provider; nocompletepack or extra centralBMS input. Update freight pernewmodulemanufacturedmass using existingonekg-route intensities,while currentnoncell hardware references remainfixed. Cell manufacture energy is includedupstream,not chargedagain. Original288kgsourcewholeHSS mass and140/190Wh/kgmetadata are historical,not the updatedengineeringvariant; complete noncell component retainedmass/yields are not certified by newmodule closure. ModulebaselineLFP149.6736kg,NMC129.316457142857kg excludesother unchangedHSSperiphery. No source systemlifetime,operatingloss,DoD orreplacement change here; issues66/67 reconcilethose separately. This fixedhomecell-design path does not silently inheritmobile futuredensitylearning. Existing legacykgmoduleprovidersremainavailable forother consumers. No native/runtime edits or recyclingcredits; omitteddevice-specificEOL remains explicitgap. Currentreference:chemistryLFP,nominal14.4kWh,cell specific energy160.0Wh/kg,installedcellmass90.0kg,modulenoncellmass59.6736kg,totalmodulemass149.6736kg.
+          <t>APPROVED HOME-STORAGE COMPONENT LIFE BUDGETS, issue67,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899 Table3,minimum/maximum calendar and cyclelife. Recompute for retained13years/2500cycles,NOT copy published20year/7300cycle factors. For eachcomponent selecthigh/lowmanufacturedsets=max(1,systemyears/componentyears,systemcycles/componentcycles),usingpairedlow/highlife endpoints,then midpointsets as engineeringexpectedlifetimeattribution. Clampatonebecauseanewcompleteinstalledsetisrequired; no assumedreusecredit for residualcomponentlife. This is not a probabilisticfailure distribution or literal fractionalinstallation. ReferenceLFPcellsets1,NMC811cellsets1.125;charger/inverter/controls/moduleBMSsets1.3125;cables1.15;housing/module steel1.0. Sourcepublished1.96/2.43cell and1.92electronics factors refer20years/7300cycles andmustnot be blindly transferred. Each home system activity now means an installeddesignplusits13yearmanufacturingreplacementbudget; labelsnominalkWhstayinstalledcapacity,not manufacturedcapacitysum. Multiplycellmanufactureonly bycellfactor within newunitmodule; moduleBMS follows electronicsfactor,modulesteel/rolling remainoneinstalledset. Externalsteelhousingremainsone,externalcontroller/electronics,charger,inverter andcablesfollowtheir own factors. Do not multiplythewholemodule anditscellsagain or buyanotherfullhome systemfor inverterfailure. Increasecomponentfreight withactualmanufacturedcomponentmass; retaininitialassemblyelectricityonce because source replacementassemblyenergy is unspecified,which remains a coveragegap. Existing servicewrapperstays1/consumerlifetimekWh fromissue66; operatingelectricity,DoD,nominalinstalledcapacity andcalendarhorizonunchanged. Transportation is at original routeintensities; packaging/maintenance labour and returntransport are gaps. Device-specific treatment/recycling is not invented; no recoverycredits orprimarysecondaryshares added. Future electronicsdurability is a sourceassumption,not verifiedmodernfleetlife. Sensitivityuseslistedmin/maxsets andsourcecalendar/cyclelimits. Numericreference:{"LFP":{"min_sets":1,"max_sets":1,"reference_sets":1.0},"NMC811":{"min_sets":1,"max_sets":1.25,"reference_sets":1.125},"electronics":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"inverter":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"charger":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"cable":{"min_sets":1,"max_sets":1.3,"reference_sets":1.15},"housing":{"min_sets":1,"max_sets":1,"reference_sets":1.0}}
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED HOME-STORAGE CELL/CAPACITY RECONCILIATION, issue65,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells. Retain labelled14.4kWhLFP and19.5kWhNMC811 grossnominalcapacity. Previous161.28kgmodule*0.63=101.6064kgcells produces14.224896/19.305216kWh even at copied140/190Wh/kg,and the actually linkedgenericcell reference is different again. Adopt the already accepted chemistry-specific160/280Wh/kg reference,so manufacture90kgLFPcells or69.642857142857kgNMC811cells per installedhome system. This selects a coherent currentcell-reference variant; it is NOT evidence original sourcecapacity or measuredcellmass were wrong. Source-specific Mohr cell inventories and precise pouch geometry remain a comparison gap. Preserve54.8352kgmodule steel,4.8384kg moduleBMS and their existingmanufacturing/transport proxies as fixed engineeringhousing architecture; do not fill releasedcellmass with arbitrarymetal tohold161.28kg. New moduleprovider is oneunit for allinstalledmodules in onehome system,not onekg or onephysicalcell. Retain exactcell supplier/product/location from corrected chemistry hardware provider; nocompletepack or extra centralBMS input. Update freight pernewmodulemanufacturedmass using existingonekg-route intensities,while currentnoncell hardware references remainfixed. Cell manufacture energy is includedupstream,not chargedagain. Original288kgsourcewholeHSS mass and140/190Wh/kgmetadata are historical,not the updatedengineeringvariant; complete noncell component retainedmass/yields are not certified by newmodule closure. ModulebaselineLFP149.6736kg,NMC129.316457142857kg excludesother unchangedHSSperiphery. No source systemlifetime,operatingloss,DoD orreplacement change here; issues66/67 reconcilethose separately. This fixedhomecell-design path does not silently inheritmobile futuredensitylearning. Existing legacykgmoduleprovidersremainavailable forother consumers. No native/runtime edits or recyclingcredits; omitteddevice-specificEOL remains explicitgap. Currentreference:chemistryLFP,nominal14.4kWh,cell specific energy160.0Wh/kg,installedcellmass90.0kg,modulenoncellmass59.6736kg,totalmodulemass149.6736kg.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 Life cycle assessment (LCA) of a battery home storage system based on primary data, Friedrich B. Jasper, Jana Spathe, Manuel Baumann, Jens F. Peters, Janna Ruhland, Marcel Weil, 2020, Journal of Cleaner Production
 Cell type: LFP, Energy density in Wh/kg:140, Cycle lifetime: 2500-10000, Calendar lifetime in years:13-20, Efficiency in %: 93, Development stage: Mature, Storage Capacity of the HSS in kWh:14.4. Weight: 288 kg.
@@ -1630,7 +1632,7 @@
         <v>86</v>
       </c>
       <c r="C38">
-        <v>14.4</v>
+        <v>18.900000000000002</v>
       </c>
       <c r="D38" t="s">
         <v>76</v>
@@ -1653,7 +1655,7 @@
         <v>10</v>
       </c>
       <c r="C39">
-        <v>8.64</v>
+        <v>9.936</v>
       </c>
       <c r="D39" t="s">
         <v>76</v>
@@ -1699,7 +1701,7 @@
         <v>12</v>
       </c>
       <c r="C41">
-        <v>0.57600000000000007</v>
+        <v>0.7560000000000001</v>
       </c>
       <c r="D41" t="s">
         <v>76</v>
@@ -1745,7 +1747,7 @@
         <v>88</v>
       </c>
       <c r="C43">
-        <v>17.28</v>
+        <v>22.68</v>
       </c>
       <c r="D43" t="s">
         <v>76</v>
@@ -1799,7 +1801,7 @@
         <v>120</v>
       </c>
       <c r="C45">
-        <v>5.76</v>
+        <v>7.56</v>
       </c>
       <c r="D45" t="s">
         <v>76</v>
@@ -1822,7 +1824,7 @@
         <v>13</v>
       </c>
       <c r="C46">
-        <v>86.399999999999991</v>
+        <v>90.3528</v>
       </c>
       <c r="D46" t="s">
         <v>78</v>
@@ -1883,7 +1885,9 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>APPROVED HOME-STORAGE CELL/CAPACITY RECONCILIATION, issue65,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells. Retain labelled14.4kWhLFP and19.5kWhNMC811 grossnominalcapacity. Previous161.28kgmodule*0.63=101.6064kgcells produces14.224896/19.305216kWh even at copied140/190Wh/kg,and the actually linkedgenericcell reference is different again. Adopt the already accepted chemistry-specific160/280Wh/kg reference,so manufacture90kgLFPcells or69.642857142857kgNMC811cells per installedhome system. This selects a coherent currentcell-reference variant; it is NOT evidence original sourcecapacity or measuredcellmass were wrong. Source-specific Mohr cell inventories and precise pouch geometry remain a comparison gap. Preserve54.8352kgmodule steel,4.8384kg moduleBMS and their existingmanufacturing/transport proxies as fixed engineeringhousing architecture; do not fill releasedcellmass with arbitrarymetal tohold161.28kg. New moduleprovider is oneunit for allinstalledmodules in onehome system,not onekg or onephysicalcell. Retain exactcell supplier/product/location from corrected chemistry hardware provider; nocompletepack or extra centralBMS input. Update freight pernewmodulemanufacturedmass using existingonekg-route intensities,while currentnoncell hardware references remainfixed. Cell manufacture energy is includedupstream,not chargedagain. Original288kgsourcewholeHSS mass and140/190Wh/kgmetadata are historical,not the updatedengineeringvariant; complete noncell component retainedmass/yields are not certified by newmodule closure. ModulebaselineLFP149.6736kg,NMC129.316457142857kg excludesother unchangedHSSperiphery. No source systemlifetime,operatingloss,DoD orreplacement change here; issues66/67 reconcilethose separately. This fixedhomecell-design path does not silently inheritmobile futuredensitylearning. Existing legacykgmoduleprovidersremainavailable forother consumers. No native/runtime edits or recyclingcredits; omitteddevice-specificEOL remains explicitgap. Currentreference:chemistryNMC811,nominal19.5kWh,cell specific energy280.0Wh/kg,installedcellmass69.64285714285714kg,modulenoncellmass59.6736kg,totalmodulemass129.31645714285713kg.
+          <t>APPROVED HOME-STORAGE COMPONENT LIFE BUDGETS, issue67,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899 Table3,minimum/maximum calendar and cyclelife. Recompute for retained13years/2500cycles,NOT copy published20year/7300cycle factors. For eachcomponent selecthigh/lowmanufacturedsets=max(1,systemyears/componentyears,systemcycles/componentcycles),usingpairedlow/highlife endpoints,then midpointsets as engineeringexpectedlifetimeattribution. Clampatonebecauseanewcompleteinstalledsetisrequired; no assumedreusecredit for residualcomponentlife. This is not a probabilisticfailure distribution or literal fractionalinstallation. ReferenceLFPcellsets1,NMC811cellsets1.125;charger/inverter/controls/moduleBMSsets1.3125;cables1.15;housing/module steel1.0. Sourcepublished1.96/2.43cell and1.92electronics factors refer20years/7300cycles andmustnot be blindly transferred. Each home system activity now means an installeddesignplusits13yearmanufacturingreplacementbudget; labelsnominalkWhstayinstalledcapacity,not manufacturedcapacitysum. Multiplycellmanufactureonly bycellfactor within newunitmodule; moduleBMS follows electronicsfactor,modulesteel/rolling remainoneinstalledset. Externalsteelhousingremainsone,externalcontroller/electronics,charger,inverter andcablesfollowtheir own factors. Do not multiplythewholemodule anditscellsagain or buyanotherfullhome systemfor inverterfailure. Increasecomponentfreight withactualmanufacturedcomponentmass; retaininitialassemblyelectricityonce because source replacementassemblyenergy is unspecified,which remains a coveragegap. Existing servicewrapperstays1/consumerlifetimekWh fromissue66; operatingelectricity,DoD,nominalinstalledcapacity andcalendarhorizonunchanged. Transportation is at original routeintensities; packaging/maintenance labour and returntransport are gaps. Device-specific treatment/recycling is not invented; no recoverycredits orprimarysecondaryshares added. Future electronicsdurability is a sourceassumption,not verifiedmodernfleetlife. Sensitivityuseslistedmin/maxsets andsourcecalendar/cyclelimits. Numericreference:{"LFP":{"min_sets":1,"max_sets":1,"reference_sets":1.0},"NMC811":{"min_sets":1,"max_sets":1.25,"reference_sets":1.125},"electronics":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"inverter":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"charger":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"cable":{"min_sets":1,"max_sets":1.3,"reference_sets":1.15},"housing":{"min_sets":1,"max_sets":1,"reference_sets":1.0}}
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED HOME-STORAGE CELL/CAPACITY RECONCILIATION, issue65,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells. Retain labelled14.4kWhLFP and19.5kWhNMC811 grossnominalcapacity. Previous161.28kgmodule*0.63=101.6064kgcells produces14.224896/19.305216kWh even at copied140/190Wh/kg,and the actually linkedgenericcell reference is different again. Adopt the already accepted chemistry-specific160/280Wh/kg reference,so manufacture90kgLFPcells or69.642857142857kgNMC811cells per installedhome system. This selects a coherent currentcell-reference variant; it is NOT evidence original sourcecapacity or measuredcellmass were wrong. Source-specific Mohr cell inventories and precise pouch geometry remain a comparison gap. Preserve54.8352kgmodule steel,4.8384kg moduleBMS and their existingmanufacturing/transport proxies as fixed engineeringhousing architecture; do not fill releasedcellmass with arbitrarymetal tohold161.28kg. New moduleprovider is oneunit for allinstalledmodules in onehome system,not onekg or onephysicalcell. Retain exactcell supplier/product/location from corrected chemistry hardware provider; nocompletepack or extra centralBMS input. Update freight pernewmodulemanufacturedmass using existingonekg-route intensities,while currentnoncell hardware references remainfixed. Cell manufacture energy is includedupstream,not chargedagain. Original288kgsourcewholeHSS mass and140/190Wh/kgmetadata are historical,not the updatedengineeringvariant; complete noncell component retainedmass/yields are not certified by newmodule closure. ModulebaselineLFP149.6736kg,NMC129.316457142857kg excludesother unchangedHSSperiphery. No source systemlifetime,operatingloss,DoD orreplacement change here; issues66/67 reconcilethose separately. This fixedhomecell-design path does not silently inheritmobile futuredensitylearning. Existing legacykgmoduleprovidersremainavailable forother consumers. No native/runtime edits or recyclingcredits; omitteddevice-specificEOL remains explicitgap. Currentreference:chemistryNMC811,nominal19.5kWh,cell specific energy280.0Wh/kg,installedcellmass69.64285714285714kg,modulenoncellmass59.6736kg,totalmodulemass129.31645714285713kg.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 Life cycle assessment (LCA) of a battery home storage system based on primary data, Friedrich B. Jasper, Jana Spathe, Manuel Baumann, Jens F. Peters, Janna Ruhland, Marcel Weil, 2020, Journal of Cleaner Production
 Cell type: LFP, Energy density in Wh/kg:140, Cycle lifetime: 2500-10000, Calendar lifetime in years:13-20, Efficiency in %: 93, Development stage: Mature, Storage Capacity of the HSS in kWh:14.4. Weight: 288 kg.
@@ -1957,7 +1961,7 @@
         <v>86</v>
       </c>
       <c r="C57">
-        <v>14.4</v>
+        <v>18.900000000000002</v>
       </c>
       <c r="D57" t="s">
         <v>76</v>
@@ -1980,7 +1984,7 @@
         <v>10</v>
       </c>
       <c r="C58">
-        <v>8.64</v>
+        <v>9.936</v>
       </c>
       <c r="D58" t="s">
         <v>76</v>
@@ -2026,7 +2030,7 @@
         <v>12</v>
       </c>
       <c r="C60">
-        <v>0.57600000000000007</v>
+        <v>0.7560000000000001</v>
       </c>
       <c r="D60" t="s">
         <v>76</v>
@@ -2072,7 +2076,7 @@
         <v>88</v>
       </c>
       <c r="C62">
-        <v>17.28</v>
+        <v>22.68</v>
       </c>
       <c r="D62" t="s">
         <v>76</v>
@@ -2126,7 +2130,7 @@
         <v>120</v>
       </c>
       <c r="C64">
-        <v>5.76</v>
+        <v>7.56</v>
       </c>
       <c r="D64" t="s">
         <v>76</v>
@@ -2149,7 +2153,7 @@
         <v>13</v>
       </c>
       <c r="C65">
-        <v>86.399999999999991</v>
+        <v>90.3528</v>
       </c>
       <c r="D65" t="s">
         <v>78</v>
@@ -4580,7 +4584,9 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>APPROVED HOME-STORAGE CELL/CAPACITY RECONCILIATION, issue65,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells. Retain labelled14.4kWhLFP and19.5kWhNMC811 grossnominalcapacity. Previous161.28kgmodule*0.63=101.6064kgcells produces14.224896/19.305216kWh even at copied140/190Wh/kg,and the actually linkedgenericcell reference is different again. Adopt the already accepted chemistry-specific160/280Wh/kg reference,so manufacture90kgLFPcells or69.642857142857kgNMC811cells per installedhome system. This selects a coherent currentcell-reference variant; it is NOT evidence original sourcecapacity or measuredcellmass were wrong. Source-specific Mohr cell inventories and precise pouch geometry remain a comparison gap. Preserve54.8352kgmodule steel,4.8384kg moduleBMS and their existingmanufacturing/transport proxies as fixed engineeringhousing architecture; do not fill releasedcellmass with arbitrarymetal tohold161.28kg. New moduleprovider is oneunit for allinstalledmodules in onehome system,not onekg or onephysicalcell. Retain exactcell supplier/product/location from corrected chemistry hardware provider; nocompletepack or extra centralBMS input. Update freight pernewmodulemanufacturedmass using existingonekg-route intensities,while currentnoncell hardware references remainfixed. Cell manufacture energy is includedupstream,not chargedagain. Original288kgsourcewholeHSS mass and140/190Wh/kgmetadata are historical,not the updatedengineeringvariant; complete noncell component retainedmass/yields are not certified by newmodule closure. ModulebaselineLFP149.6736kg,NMC129.316457142857kg excludesother unchangedHSSperiphery. No source systemlifetime,operatingloss,DoD orreplacement change here; issues66/67 reconcilethose separately. This fixedhomecell-design path does not silently inheritmobile futuredensitylearning. Existing legacykgmoduleprovidersremainavailable forother consumers. No native/runtime edits or recyclingcredits; omitteddevice-specificEOL remains explicitgap.</t>
+          <t>APPROVED HOME-STORAGE COMPONENT LIFE BUDGETS, issue67,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899 Table3,minimum/maximum calendar and cyclelife. Recompute for retained13years/2500cycles,NOT copy published20year/7300cycle factors. For eachcomponent selecthigh/lowmanufacturedsets=max(1,systemyears/componentyears,systemcycles/componentcycles),usingpairedlow/highlife endpoints,then midpointsets as engineeringexpectedlifetimeattribution. Clampatonebecauseanewcompleteinstalledsetisrequired; no assumedreusecredit for residualcomponentlife. This is not a probabilisticfailure distribution or literal fractionalinstallation. ReferenceLFPcellsets1,NMC811cellsets1.125;charger/inverter/controls/moduleBMSsets1.3125;cables1.15;housing/module steel1.0. Sourcepublished1.96/2.43cell and1.92electronics factors refer20years/7300cycles andmustnot be blindly transferred. Each home system activity now means an installeddesignplusits13yearmanufacturingreplacementbudget; labelsnominalkWhstayinstalledcapacity,not manufacturedcapacitysum. Multiplycellmanufactureonly bycellfactor within newunitmodule; moduleBMS follows electronicsfactor,modulesteel/rolling remainoneinstalledset. Externalsteelhousingremainsone,externalcontroller/electronics,charger,inverter andcablesfollowtheir own factors. Do not multiplythewholemodule anditscellsagain or buyanotherfullhome systemfor inverterfailure. Increasecomponentfreight withactualmanufacturedcomponentmass; retaininitialassemblyelectricityonce because source replacementassemblyenergy is unspecified,which remains a coveragegap. Existing servicewrapperstays1/consumerlifetimekWh fromissue66; operatingelectricity,DoD,nominalinstalledcapacity andcalendarhorizonunchanged. Transportation is at original routeintensities; packaging/maintenance labour and returntransport are gaps. Device-specific treatment/recycling is not invented; no recoverycredits orprimarysecondaryshares added. Future electronicsdurability is a sourceassumption,not verifiedmodernfleetlife. Sensitivityuseslistedmin/maxsets andsourcecalendar/cyclelimits. Numericreference:{"LFP":{"min_sets":1,"max_sets":1,"reference_sets":1.0},"NMC811":{"min_sets":1,"max_sets":1.25,"reference_sets":1.125},"electronics":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"inverter":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"charger":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"cable":{"min_sets":1,"max_sets":1.3,"reference_sets":1.15},"housing":{"min_sets":1,"max_sets":1,"reference_sets":1.0}}
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED HOME-STORAGE CELL/CAPACITY RECONCILIATION, issue65,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells. Retain labelled14.4kWhLFP and19.5kWhNMC811 grossnominalcapacity. Previous161.28kgmodule*0.63=101.6064kgcells produces14.224896/19.305216kWh even at copied140/190Wh/kg,and the actually linkedgenericcell reference is different again. Adopt the already accepted chemistry-specific160/280Wh/kg reference,so manufacture90kgLFPcells or69.642857142857kgNMC811cells per installedhome system. This selects a coherent currentcell-reference variant; it is NOT evidence original sourcecapacity or measuredcellmass were wrong. Source-specific Mohr cell inventories and precise pouch geometry remain a comparison gap. Preserve54.8352kgmodule steel,4.8384kg moduleBMS and their existingmanufacturing/transport proxies as fixed engineeringhousing architecture; do not fill releasedcellmass with arbitrarymetal tohold161.28kg. New moduleprovider is oneunit for allinstalledmodules in onehome system,not onekg or onephysicalcell. Retain exactcell supplier/product/location from corrected chemistry hardware provider; nocompletepack or extra centralBMS input. Update freight pernewmodulemanufacturedmass using existingonekg-route intensities,while currentnoncell hardware references remainfixed. Cell manufacture energy is includedupstream,not chargedagain. Original288kgsourcewholeHSS mass and140/190Wh/kgmetadata are historical,not the updatedengineeringvariant; complete noncell component retainedmass/yields are not certified by newmodule closure. ModulebaselineLFP149.6736kg,NMC129.316457142857kg excludesother unchangedHSSperiphery. No source systemlifetime,operatingloss,DoD orreplacement change here; issues66/67 reconcilethose separately. This fixedhomecell-design path does not silently inheritmobile futuredensitylearning. Existing legacykgmoduleprovidersremainavailable forother consumers. No native/runtime edits or recyclingcredits; omitteddevice-specificEOL remains explicitgap.</t>
         </is>
       </c>
     </row>
@@ -4680,7 +4686,7 @@
         </is>
       </c>
       <c r="B225">
-        <v>4.8384</v>
+        <v>6.3504000000000005</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -4820,7 +4826,7 @@
         </is>
       </c>
       <c r="B229">
-        <v>149.6736</v>
+        <v>151.1856</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -4855,7 +4861,7 @@
         </is>
       </c>
       <c r="B230">
-        <v>149.6736</v>
+        <v>151.1856</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -4890,7 +4896,7 @@
         </is>
       </c>
       <c r="B231">
-        <v>1197.3888</v>
+        <v>1209.4848</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -4996,7 +5002,9 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>APPROVED HOME-STORAGE CELL/CAPACITY RECONCILIATION, issue65,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells. Retain labelled14.4kWhLFP and19.5kWhNMC811 grossnominalcapacity. Previous161.28kgmodule*0.63=101.6064kgcells produces14.224896/19.305216kWh even at copied140/190Wh/kg,and the actually linkedgenericcell reference is different again. Adopt the already accepted chemistry-specific160/280Wh/kg reference,so manufacture90kgLFPcells or69.642857142857kgNMC811cells per installedhome system. This selects a coherent currentcell-reference variant; it is NOT evidence original sourcecapacity or measuredcellmass were wrong. Source-specific Mohr cell inventories and precise pouch geometry remain a comparison gap. Preserve54.8352kgmodule steel,4.8384kg moduleBMS and their existingmanufacturing/transport proxies as fixed engineeringhousing architecture; do not fill releasedcellmass with arbitrarymetal tohold161.28kg. New moduleprovider is oneunit for allinstalledmodules in onehome system,not onekg or onephysicalcell. Retain exactcell supplier/product/location from corrected chemistry hardware provider; nocompletepack or extra centralBMS input. Update freight pernewmodulemanufacturedmass using existingonekg-route intensities,while currentnoncell hardware references remainfixed. Cell manufacture energy is includedupstream,not chargedagain. Original288kgsourcewholeHSS mass and140/190Wh/kgmetadata are historical,not the updatedengineeringvariant; complete noncell component retainedmass/yields are not certified by newmodule closure. ModulebaselineLFP149.6736kg,NMC129.316457142857kg excludesother unchangedHSSperiphery. No source systemlifetime,operatingloss,DoD orreplacement change here; issues66/67 reconcilethose separately. This fixedhomecell-design path does not silently inheritmobile futuredensitylearning. Existing legacykgmoduleprovidersremainavailable forother consumers. No native/runtime edits or recyclingcredits; omitteddevice-specificEOL remains explicitgap.</t>
+          <t>APPROVED HOME-STORAGE COMPONENT LIFE BUDGETS, issue67,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899 Table3,minimum/maximum calendar and cyclelife. Recompute for retained13years/2500cycles,NOT copy published20year/7300cycle factors. For eachcomponent selecthigh/lowmanufacturedsets=max(1,systemyears/componentyears,systemcycles/componentcycles),usingpairedlow/highlife endpoints,then midpointsets as engineeringexpectedlifetimeattribution. Clampatonebecauseanewcompleteinstalledsetisrequired; no assumedreusecredit for residualcomponentlife. This is not a probabilisticfailure distribution or literal fractionalinstallation. ReferenceLFPcellsets1,NMC811cellsets1.125;charger/inverter/controls/moduleBMSsets1.3125;cables1.15;housing/module steel1.0. Sourcepublished1.96/2.43cell and1.92electronics factors refer20years/7300cycles andmustnot be blindly transferred. Each home system activity now means an installeddesignplusits13yearmanufacturingreplacementbudget; labelsnominalkWhstayinstalledcapacity,not manufacturedcapacitysum. Multiplycellmanufactureonly bycellfactor within newunitmodule; moduleBMS follows electronicsfactor,modulesteel/rolling remainoneinstalledset. Externalsteelhousingremainsone,externalcontroller/electronics,charger,inverter andcablesfollowtheir own factors. Do not multiplythewholemodule anditscellsagain or buyanotherfullhome systemfor inverterfailure. Increasecomponentfreight withactualmanufacturedcomponentmass; retaininitialassemblyelectricityonce because source replacementassemblyenergy is unspecified,which remains a coveragegap. Existing servicewrapperstays1/consumerlifetimekWh fromissue66; operatingelectricity,DoD,nominalinstalledcapacity andcalendarhorizonunchanged. Transportation is at original routeintensities; packaging/maintenance labour and returntransport are gaps. Device-specific treatment/recycling is not invented; no recoverycredits orprimarysecondaryshares added. Future electronicsdurability is a sourceassumption,not verifiedmodernfleetlife. Sensitivityuseslistedmin/maxsets andsourcecalendar/cyclelimits. Numericreference:{"LFP":{"min_sets":1,"max_sets":1,"reference_sets":1.0},"NMC811":{"min_sets":1,"max_sets":1.25,"reference_sets":1.125},"electronics":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"inverter":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"charger":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"cable":{"min_sets":1,"max_sets":1.3,"reference_sets":1.15},"housing":{"min_sets":1,"max_sets":1,"reference_sets":1.0}}
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED HOME-STORAGE CELL/CAPACITY RECONCILIATION, issue65,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells. Retain labelled14.4kWhLFP and19.5kWhNMC811 grossnominalcapacity. Previous161.28kgmodule*0.63=101.6064kgcells produces14.224896/19.305216kWh even at copied140/190Wh/kg,and the actually linkedgenericcell reference is different again. Adopt the already accepted chemistry-specific160/280Wh/kg reference,so manufacture90kgLFPcells or69.642857142857kgNMC811cells per installedhome system. This selects a coherent currentcell-reference variant; it is NOT evidence original sourcecapacity or measuredcellmass were wrong. Source-specific Mohr cell inventories and precise pouch geometry remain a comparison gap. Preserve54.8352kgmodule steel,4.8384kg moduleBMS and their existingmanufacturing/transport proxies as fixed engineeringhousing architecture; do not fill releasedcellmass with arbitrarymetal tohold161.28kg. New moduleprovider is oneunit for allinstalledmodules in onehome system,not onekg or onephysicalcell. Retain exactcell supplier/product/location from corrected chemistry hardware provider; nocompletepack or extra centralBMS input. Update freight pernewmodulemanufacturedmass using existingonekg-route intensities,while currentnoncell hardware references remainfixed. Cell manufacture energy is includedupstream,not chargedagain. Original288kgsourcewholeHSS mass and140/190Wh/kgmetadata are historical,not the updatedengineeringvariant; complete noncell component retainedmass/yields are not certified by newmodule closure. ModulebaselineLFP149.6736kg,NMC129.316457142857kg excludesother unchangedHSSperiphery. No source systemlifetime,operatingloss,DoD orreplacement change here; issues66/67 reconcilethose separately. This fixedhomecell-design path does not silently inheritmobile futuredensitylearning. Existing legacykgmoduleprovidersremainavailable forother consumers. No native/runtime edits or recyclingcredits; omitteddevice-specificEOL remains explicitgap.</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5104,7 @@
         </is>
       </c>
       <c r="B244">
-        <v>4.8384</v>
+        <v>6.3504000000000005</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -5131,7 +5139,7 @@
         </is>
       </c>
       <c r="B245">
-        <v>69.64285714285714</v>
+        <v>78.34821428571428</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -5236,7 +5244,7 @@
         </is>
       </c>
       <c r="B248">
-        <v>129.31645714285713</v>
+        <v>139.53381428571427</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -5271,7 +5279,7 @@
         </is>
       </c>
       <c r="B249">
-        <v>129.31645714285713</v>
+        <v>139.53381428571427</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -5306,7 +5314,7 @@
         </is>
       </c>
       <c r="B250">
-        <v>1034.531657142857</v>
+        <v>1116.2705142857142</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>

--- a/premise/data/additional_inventories/lci-home-batteries.xlsx
+++ b/premise/data/additional_inventories/lci-home-batteries.xlsx
@@ -1765,12 +1765,12 @@
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cell modules, home 14.4kWh LFP, capacity-consistent reference</t>
+          <t xml:space="preserve">battery module production, home storage, Li-ion, LFP, 14.4 kWh</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>cell modules, home 14.4kWh LFP, capacity-consistent reference</t>
+          <t xml:space="preserve">battery module, home storage, Li-ion, LFP, 14.4 kWh</t>
         </is>
       </c>
       <c r="C44">
@@ -2094,12 +2094,12 @@
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="inlineStr">
         <is>
-          <t>cell modules, home 19.5kWh NMC811, capacity-consistent reference</t>
+          <t xml:space="preserve">battery module production, home storage, Li-ion, NMC811, 19.5 kWh</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>cell modules, home 19.5kWh NMC811, capacity-consistent reference</t>
+          <t xml:space="preserve">battery module, home storage, Li-ion, NMC811, 19.5 kWh</t>
         </is>
       </c>
       <c r="C63">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>cell modules, home 14.4kWh LFP, capacity-consistent reference</t>
+          <t xml:space="preserve">battery module production, home storage, Li-ion, LFP, 14.4 kWh</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>cell modules, home 14.4kWh LFP, capacity-consistent reference</t>
+          <t xml:space="preserve">battery module, home storage, Li-ion, LFP, 14.4 kWh</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,8 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>APPROVED HOME-STORAGE COMPONENT LIFE BUDGETS, issue67,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899 Table3,minimum/maximum calendar and cyclelife. Recompute for retained13years/2500cycles,NOT copy published20year/7300cycle factors. For eachcomponent selecthigh/lowmanufacturedsets=max(1,systemyears/componentyears,systemcycles/componentcycles),usingpairedlow/highlife endpoints,then midpointsets as engineeringexpectedlifetimeattribution. Clampatonebecauseanewcompleteinstalledsetisrequired; no assumedreusecredit for residualcomponentlife. This is not a probabilisticfailure distribution or literal fractionalinstallation. ReferenceLFPcellsets1,NMC811cellsets1.125;charger/inverter/controls/moduleBMSsets1.3125;cables1.15;housing/module steel1.0. Sourcepublished1.96/2.43cell and1.92electronics factors refer20years/7300cycles andmustnot be blindly transferred. Each home system activity now means an installeddesignplusits13yearmanufacturingreplacementbudget; labelsnominalkWhstayinstalledcapacity,not manufacturedcapacitysum. Multiplycellmanufactureonly bycellfactor within newunitmodule; moduleBMS follows electronicsfactor,modulesteel/rolling remainoneinstalledset. Externalsteelhousingremainsone,externalcontroller/electronics,charger,inverter andcablesfollowtheir own factors. Do not multiplythewholemodule anditscellsagain or buyanotherfullhome systemfor inverterfailure. Increasecomponentfreight withactualmanufacturedcomponentmass; retaininitialassemblyelectricityonce because source replacementassemblyenergy is unspecified,which remains a coveragegap. Existing servicewrapperstays1/consumerlifetimekWh fromissue66; operatingelectricity,DoD,nominalinstalledcapacity andcalendarhorizonunchanged. Transportation is at original routeintensities; packaging/maintenance labour and returntransport are gaps. Device-specific treatment/recycling is not invented; no recoverycredits orprimarysecondaryshares added. Future electronicsdurability is a sourceassumption,not verifiedmodernfleetlife. Sensitivityuseslistedmin/maxsets andsourcecalendar/cyclelimits. Numericreference:{"LFP":{"min_sets":1,"max_sets":1,"reference_sets":1.0},"NMC811":{"min_sets":1,"max_sets":1.25,"reference_sets":1.125},"electronics":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"inverter":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"charger":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"cable":{"min_sets":1,"max_sets":1.3,"reference_sets":1.15},"housing":{"min_sets":1,"max_sets":1,"reference_sets":1.0}}
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: cell modules, home 14.4kWh LFP, capacity-consistent reference. Former reference product: cell modules, home 14.4kWh LFP, capacity-consistent reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED HOME-STORAGE COMPONENT LIFE BUDGETS, issue67,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899 Table3,minimum/maximum calendar and cyclelife. Recompute for retained13years/2500cycles,NOT copy published20year/7300cycle factors. For eachcomponent selecthigh/lowmanufacturedsets=max(1,systemyears/componentyears,systemcycles/componentcycles),usingpairedlow/highlife endpoints,then midpointsets as engineeringexpectedlifetimeattribution. Clampatonebecauseanewcompleteinstalledsetisrequired; no assumedreusecredit for residualcomponentlife. This is not a probabilisticfailure distribution or literal fractionalinstallation. ReferenceLFPcellsets1,NMC811cellsets1.125;charger/inverter/controls/moduleBMSsets1.3125;cables1.15;housing/module steel1.0. Sourcepublished1.96/2.43cell and1.92electronics factors refer20years/7300cycles andmustnot be blindly transferred. Each home system activity now means an installeddesignplusits13yearmanufacturingreplacementbudget; labelsnominalkWhstayinstalledcapacity,not manufacturedcapacitysum. Multiplycellmanufactureonly bycellfactor within newunitmodule; moduleBMS follows electronicsfactor,modulesteel/rolling remainoneinstalledset. Externalsteelhousingremainsone,externalcontroller/electronics,charger,inverter andcablesfollowtheir own factors. Do not multiplythewholemodule anditscellsagain or buyanotherfullhome systemfor inverterfailure. Increasecomponentfreight withactualmanufacturedcomponentmass; retaininitialassemblyelectricityonce because source replacementassemblyenergy is unspecified,which remains a coveragegap. Existing servicewrapperstays1/consumerlifetimekWh fromissue66; operatingelectricity,DoD,nominalinstalledcapacity andcalendarhorizonunchanged. Transportation is at original routeintensities; packaging/maintenance labour and returntransport are gaps. Device-specific treatment/recycling is not invented; no recoverycredits orprimarysecondaryshares added. Future electronicsdurability is a sourceassumption,not verifiedmodernfleetlife. Sensitivityuseslistedmin/maxsets andsourcecalendar/cyclelimits. Numericreference:{"LFP":{"min_sets":1,"max_sets":1,"reference_sets":1.0},"NMC811":{"min_sets":1,"max_sets":1.25,"reference_sets":1.125},"electronics":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"inverter":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"charger":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"cable":{"min_sets":1,"max_sets":1.3,"reference_sets":1.15},"housing":{"min_sets":1,"max_sets":1,"reference_sets":1.0}}
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED HOME-STORAGE CELL/CAPACITY RECONCILIATION, issue65,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells. Retain labelled14.4kWhLFP and19.5kWhNMC811 grossnominalcapacity. Previous161.28kgmodule*0.63=101.6064kgcells produces14.224896/19.305216kWh even at copied140/190Wh/kg,and the actually linkedgenericcell reference is different again. Adopt the already accepted chemistry-specific160/280Wh/kg reference,so manufacture90kgLFPcells or69.642857142857kgNMC811cells per installedhome system. This selects a coherent currentcell-reference variant; it is NOT evidence original sourcecapacity or measuredcellmass were wrong. Source-specific Mohr cell inventories and precise pouch geometry remain a comparison gap. Preserve54.8352kgmodule steel,4.8384kg moduleBMS and their existingmanufacturing/transport proxies as fixed engineeringhousing architecture; do not fill releasedcellmass with arbitrarymetal tohold161.28kg. New moduleprovider is oneunit for allinstalledmodules in onehome system,not onekg or onephysicalcell. Retain exactcell supplier/product/location from corrected chemistry hardware provider; nocompletepack or extra centralBMS input. Update freight pernewmodulemanufacturedmass using existingonekg-route intensities,while currentnoncell hardware references remainfixed. Cell manufacture energy is includedupstream,not chargedagain. Original288kgsourcewholeHSS mass and140/190Wh/kgmetadata are historical,not the updatedengineeringvariant; complete noncell component retainedmass/yields are not certified by newmodule closure. ModulebaselineLFP149.6736kg,NMC129.316457142857kg excludesother unchangedHSSperiphery. No source systemlifetime,operatingloss,DoD orreplacement change here; issues66/67 reconcilethose separately. This fixedhomecell-design path does not silently inheritmobile futuredensitylearning. Existing legacykgmoduleprovidersremainavailable forother consumers. No native/runtime edits or recyclingcredits; omitteddevice-specificEOL remains explicitgap.</t>
         </is>
@@ -4647,7 +4648,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>cell modules, home 14.4kWh LFP, capacity-consistent reference</t>
+          <t xml:space="preserve">battery module production, home storage, Li-ion, LFP, 14.4 kWh</t>
         </is>
       </c>
       <c r="B224">
@@ -4670,12 +4671,12 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>cell modules, home 14.4kWh LFP, capacity-consistent reference</t>
+          <t xml:space="preserve">battery module, home storage, Li-ion, LFP, 14.4 kWh</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>cell modules, home 14.4kWh LFP, capacity-consistent reference</t>
+          <t xml:space="preserve">battery module, home storage, Li-ion, LFP, 14.4 kWh</t>
         </is>
       </c>
     </row>
@@ -4932,7 +4933,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>cell modules, home 19.5kWh NMC811, capacity-consistent reference</t>
+          <t xml:space="preserve">battery module production, home storage, Li-ion, NMC811, 19.5 kWh</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4967,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>cell modules, home 19.5kWh NMC811, capacity-consistent reference</t>
+          <t xml:space="preserve">battery module, home storage, Li-ion, NMC811, 19.5 kWh</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5003,8 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>APPROVED HOME-STORAGE COMPONENT LIFE BUDGETS, issue67,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899 Table3,minimum/maximum calendar and cyclelife. Recompute for retained13years/2500cycles,NOT copy published20year/7300cycle factors. For eachcomponent selecthigh/lowmanufacturedsets=max(1,systemyears/componentyears,systemcycles/componentcycles),usingpairedlow/highlife endpoints,then midpointsets as engineeringexpectedlifetimeattribution. Clampatonebecauseanewcompleteinstalledsetisrequired; no assumedreusecredit for residualcomponentlife. This is not a probabilisticfailure distribution or literal fractionalinstallation. ReferenceLFPcellsets1,NMC811cellsets1.125;charger/inverter/controls/moduleBMSsets1.3125;cables1.15;housing/module steel1.0. Sourcepublished1.96/2.43cell and1.92electronics factors refer20years/7300cycles andmustnot be blindly transferred. Each home system activity now means an installeddesignplusits13yearmanufacturingreplacementbudget; labelsnominalkWhstayinstalledcapacity,not manufacturedcapacitysum. Multiplycellmanufactureonly bycellfactor within newunitmodule; moduleBMS follows electronicsfactor,modulesteel/rolling remainoneinstalledset. Externalsteelhousingremainsone,externalcontroller/electronics,charger,inverter andcablesfollowtheir own factors. Do not multiplythewholemodule anditscellsagain or buyanotherfullhome systemfor inverterfailure. Increasecomponentfreight withactualmanufacturedcomponentmass; retaininitialassemblyelectricityonce because source replacementassemblyenergy is unspecified,which remains a coveragegap. Existing servicewrapperstays1/consumerlifetimekWh fromissue66; operatingelectricity,DoD,nominalinstalledcapacity andcalendarhorizonunchanged. Transportation is at original routeintensities; packaging/maintenance labour and returntransport are gaps. Device-specific treatment/recycling is not invented; no recoverycredits orprimarysecondaryshares added. Future electronicsdurability is a sourceassumption,not verifiedmodernfleetlife. Sensitivityuseslistedmin/maxsets andsourcecalendar/cyclelimits. Numericreference:{"LFP":{"min_sets":1,"max_sets":1,"reference_sets":1.0},"NMC811":{"min_sets":1,"max_sets":1.25,"reference_sets":1.125},"electronics":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"inverter":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"charger":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"cable":{"min_sets":1,"max_sets":1.3,"reference_sets":1.15},"housing":{"min_sets":1,"max_sets":1,"reference_sets":1.0}}
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: cell modules, home 19.5kWh NMC811, capacity-consistent reference. Former reference product: cell modules, home 19.5kWh NMC811, capacity-consistent reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED HOME-STORAGE COMPONENT LIFE BUDGETS, issue67,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899 Table3,minimum/maximum calendar and cyclelife. Recompute for retained13years/2500cycles,NOT copy published20year/7300cycle factors. For eachcomponent selecthigh/lowmanufacturedsets=max(1,systemyears/componentyears,systemcycles/componentcycles),usingpairedlow/highlife endpoints,then midpointsets as engineeringexpectedlifetimeattribution. Clampatonebecauseanewcompleteinstalledsetisrequired; no assumedreusecredit for residualcomponentlife. This is not a probabilisticfailure distribution or literal fractionalinstallation. ReferenceLFPcellsets1,NMC811cellsets1.125;charger/inverter/controls/moduleBMSsets1.3125;cables1.15;housing/module steel1.0. Sourcepublished1.96/2.43cell and1.92electronics factors refer20years/7300cycles andmustnot be blindly transferred. Each home system activity now means an installeddesignplusits13yearmanufacturingreplacementbudget; labelsnominalkWhstayinstalledcapacity,not manufacturedcapacitysum. Multiplycellmanufactureonly bycellfactor within newunitmodule; moduleBMS follows electronicsfactor,modulesteel/rolling remainoneinstalledset. Externalsteelhousingremainsone,externalcontroller/electronics,charger,inverter andcablesfollowtheir own factors. Do not multiplythewholemodule anditscellsagain or buyanotherfullhome systemfor inverterfailure. Increasecomponentfreight withactualmanufacturedcomponentmass; retaininitialassemblyelectricityonce because source replacementassemblyenergy is unspecified,which remains a coveragegap. Existing servicewrapperstays1/consumerlifetimekWh fromissue66; operatingelectricity,DoD,nominalinstalledcapacity andcalendarhorizonunchanged. Transportation is at original routeintensities; packaging/maintenance labour and returntransport are gaps. Device-specific treatment/recycling is not invented; no recoverycredits orprimarysecondaryshares added. Future electronicsdurability is a sourceassumption,not verifiedmodernfleetlife. Sensitivityuseslistedmin/maxsets andsourcecalendar/cyclelimits. Numericreference:{"LFP":{"min_sets":1,"max_sets":1,"reference_sets":1.0},"NMC811":{"min_sets":1,"max_sets":1.25,"reference_sets":1.125},"electronics":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"inverter":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"charger":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"cable":{"min_sets":1,"max_sets":1.3,"reference_sets":1.15},"housing":{"min_sets":1,"max_sets":1,"reference_sets":1.0}}
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED HOME-STORAGE CELL/CAPACITY RECONCILIATION, issue65,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells. Retain labelled14.4kWhLFP and19.5kWhNMC811 grossnominalcapacity. Previous161.28kgmodule*0.63=101.6064kgcells produces14.224896/19.305216kWh even at copied140/190Wh/kg,and the actually linkedgenericcell reference is different again. Adopt the already accepted chemistry-specific160/280Wh/kg reference,so manufacture90kgLFPcells or69.642857142857kgNMC811cells per installedhome system. This selects a coherent currentcell-reference variant; it is NOT evidence original sourcecapacity or measuredcellmass were wrong. Source-specific Mohr cell inventories and precise pouch geometry remain a comparison gap. Preserve54.8352kgmodule steel,4.8384kg moduleBMS and their existingmanufacturing/transport proxies as fixed engineeringhousing architecture; do not fill releasedcellmass with arbitrarymetal tohold161.28kg. New moduleprovider is oneunit for allinstalledmodules in onehome system,not onekg or onephysicalcell. Retain exactcell supplier/product/location from corrected chemistry hardware provider; nocompletepack or extra centralBMS input. Update freight pernewmodulemanufacturedmass using existingonekg-route intensities,while currentnoncell hardware references remainfixed. Cell manufacture energy is includedupstream,not chargedagain. Original288kgsourcewholeHSS mass and140/190Wh/kgmetadata are historical,not the updatedengineeringvariant; complete noncell component retainedmass/yields are not certified by newmodule closure. ModulebaselineLFP149.6736kg,NMC129.316457142857kg excludesother unchangedHSSperiphery. No source systemlifetime,operatingloss,DoD orreplacement change here; issues66/67 reconcilethose separately. This fixedhomecell-design path does not silently inheritmobile futuredensitylearning. Existing legacykgmoduleprovidersremainavailable forother consumers. No native/runtime edits or recyclingcredits; omitteddevice-specificEOL remains explicitgap.</t>
         </is>
@@ -5065,7 +5067,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>cell modules, home 19.5kWh NMC811, capacity-consistent reference</t>
+          <t xml:space="preserve">battery module production, home storage, Li-ion, NMC811, 19.5 kWh</t>
         </is>
       </c>
       <c r="B243">
@@ -5088,12 +5090,12 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>cell modules, home 19.5kWh NMC811, capacity-consistent reference</t>
+          <t xml:space="preserve">battery module, home storage, Li-ion, NMC811, 19.5 kWh</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>cell modules, home 19.5kWh NMC811, capacity-consistent reference</t>
+          <t xml:space="preserve">battery module, home storage, Li-ion, NMC811, 19.5 kWh</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5137,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell production, Li-ion, NMC811, silicon-graphite anode</t>
         </is>
       </c>
       <c r="B245">
@@ -5158,12 +5160,12 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC811, silicon-graphite anode</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC811, silicon-graphite anode</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-home-batteries.xlsx
+++ b/premise/data/additional_inventories/lci-home-batteries.xlsx
@@ -913,7 +913,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L250"/>
+  <dimension ref="A1:L260"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.5" customWidth="1"/>
@@ -1556,7 +1556,8 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>APPROVED HOME-STORAGE COMPONENT LIFE BUDGETS, issue67,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899 Table3,minimum/maximum calendar and cyclelife. Recompute for retained13years/2500cycles,NOT copy published20year/7300cycle factors. For eachcomponent selecthigh/lowmanufacturedsets=max(1,systemyears/componentyears,systemcycles/componentcycles),usingpairedlow/highlife endpoints,then midpointsets as engineeringexpectedlifetimeattribution. Clampatonebecauseanewcompleteinstalledsetisrequired; no assumedreusecredit for residualcomponentlife. This is not a probabilisticfailure distribution or literal fractionalinstallation. ReferenceLFPcellsets1,NMC811cellsets1.125;charger/inverter/controls/moduleBMSsets1.3125;cables1.15;housing/module steel1.0. Sourcepublished1.96/2.43cell and1.92electronics factors refer20years/7300cycles andmustnot be blindly transferred. Each home system activity now means an installeddesignplusits13yearmanufacturingreplacementbudget; labelsnominalkWhstayinstalledcapacity,not manufacturedcapacitysum. Multiplycellmanufactureonly bycellfactor within newunitmodule; moduleBMS follows electronicsfactor,modulesteel/rolling remainoneinstalledset. Externalsteelhousingremainsone,externalcontroller/electronics,charger,inverter andcablesfollowtheir own factors. Do not multiplythewholemodule anditscellsagain or buyanotherfullhome systemfor inverterfailure. Increasecomponentfreight withactualmanufacturedcomponentmass; retaininitialassemblyelectricityonce because source replacementassemblyenergy is unspecified,which remains a coveragegap. Existing servicewrapperstays1/consumerlifetimekWh fromissue66; operatingelectricity,DoD,nominalinstalledcapacity andcalendarhorizonunchanged. Transportation is at original routeintensities; packaging/maintenance labour and returntransport are gaps. Device-specific treatment/recycling is not invented; no recoverycredits orprimarysecondaryshares added. Future electronicsdurability is a sourceassumption,not verifiedmodernfleetlife. Sensitivityuseslistedmin/maxsets andsourcecalendar/cyclelimits. Numericreference:{"LFP":{"min_sets":1,"max_sets":1,"reference_sets":1.0},"NMC811":{"min_sets":1,"max_sets":1.25,"reference_sets":1.125},"electronics":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"inverter":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"charger":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"cable":{"min_sets":1,"max_sets":1.3,"reference_sets":1.15},"housing":{"min_sets":1,"max_sets":1,"reference_sets":1.0}}
+          <t xml:space="preserve">HOME-STORAGE END-OF-LIFE COVERAGE, 2026-10-19. Add terminal treatment at this complete-system lifetime-budget level only. Finished cells 90 kg; charger, inverter, controller, separate control electronics and module BMS 56.2464 kg; cables 9.936 kg; structural steel 138.10464 kg; housing rubber 0.25056 kg. Total 294.5376 kg matches lifetime manufactured finished components. Existing replacement factors are already included in these purchases; do not apply them again. Housing is split using its existing 99.7% steel/0.3% rubber recipe; module steel is separate. Electronics are routed as finished devices, not counted again as constituent metals. Cells retain the existing generic Li-ion waste-market proxy; electronics, wiring, bulk iron and rubber use their existing waste treatment markets. These are documented treatment/geography proxies (GLO battery; RoW other waste markets) for the RER home system, not device-specific measured recovery yields or a Swiss disposal mix. Native market treatment/recovery conventions are retained without adding independent material substitution credits or new primary/secondary assumptions. Negative kg technosphere amounts send discarded products to waste markets whose reference production is -1 kg. Manufacturing process services/losses are not added to retained final-product waste. All lifetime-manufactured components are assigned eventual treatment in this attributional lifecycle reference; timing, reuse and remaining life are not dynamically modelled. Existing operational energy, nominal capacity, manufacturing, replacement factors and lifetime output remain unchanged. No additional whole-battery-capacity purchase or disassembly/EOL helper is added upstream. The following historical omission notes are superseded by this explicit treatment addition.
+APPROVED HOME-STORAGE COMPONENT LIFE BUDGETS, issue67,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899 Table3,minimum/maximum calendar and cyclelife. Recompute for retained13years/2500cycles,NOT copy published20year/7300cycle factors. For eachcomponent selecthigh/lowmanufacturedsets=max(1,systemyears/componentyears,systemcycles/componentcycles),usingpairedlow/highlife endpoints,then midpointsets as engineeringexpectedlifetimeattribution. Clampatonebecauseanewcompleteinstalledsetisrequired; no assumedreusecredit for residualcomponentlife. This is not a probabilisticfailure distribution or literal fractionalinstallation. ReferenceLFPcellsets1,NMC811cellsets1.125;charger/inverter/controls/moduleBMSsets1.3125;cables1.15;housing/module steel1.0. Sourcepublished1.96/2.43cell and1.92electronics factors refer20years/7300cycles andmustnot be blindly transferred. Each home system activity now means an installeddesignplusits13yearmanufacturingreplacementbudget; labelsnominalkWhstayinstalledcapacity,not manufacturedcapacitysum. Multiplycellmanufactureonly bycellfactor within newunitmodule; moduleBMS follows electronicsfactor,modulesteel/rolling remainoneinstalledset. Externalsteelhousingremainsone,externalcontroller/electronics,charger,inverter andcablesfollowtheir own factors. Do not multiplythewholemodule anditscellsagain or buyanotherfullhome systemfor inverterfailure. Increasecomponentfreight withactualmanufacturedcomponentmass; retaininitialassemblyelectricityonce because source replacementassemblyenergy is unspecified,which remains a coveragegap. Existing servicewrapperstays1/consumerlifetimekWh fromissue66; operatingelectricity,DoD,nominalinstalledcapacity andcalendarhorizonunchanged. Transportation is at original routeintensities; packaging/maintenance labour and returntransport are gaps. Device-specific treatment/recycling is not invented; no recoverycredits orprimarysecondaryshares added. Future electronicsdurability is a sourceassumption,not verifiedmodernfleetlife. Sensitivityuseslistedmin/maxsets andsourcecalendar/cyclelimits. Numericreference:{"LFP":{"min_sets":1,"max_sets":1,"reference_sets":1.0},"NMC811":{"min_sets":1,"max_sets":1.25,"reference_sets":1.125},"electronics":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"inverter":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"charger":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"cable":{"min_sets":1,"max_sets":1.3,"reference_sets":1.15},"housing":{"min_sets":1,"max_sets":1,"reference_sets":1.0}}
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED HOME-STORAGE CELL/CAPACITY RECONCILIATION, issue65,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells. Retain labelled14.4kWhLFP and19.5kWhNMC811 grossnominalcapacity. Previous161.28kgmodule*0.63=101.6064kgcells produces14.224896/19.305216kWh even at copied140/190Wh/kg,and the actually linkedgenericcell reference is different again. Adopt the already accepted chemistry-specific160/280Wh/kg reference,so manufacture90kgLFPcells or69.642857142857kgNMC811cells per installedhome system. This selects a coherent currentcell-reference variant; it is NOT evidence original sourcecapacity or measuredcellmass were wrong. Source-specific Mohr cell inventories and precise pouch geometry remain a comparison gap. Preserve54.8352kgmodule steel,4.8384kg moduleBMS and their existingmanufacturing/transport proxies as fixed engineeringhousing architecture; do not fill releasedcellmass with arbitrarymetal tohold161.28kg. New moduleprovider is oneunit for allinstalledmodules in onehome system,not onekg or onephysicalcell. Retain exactcell supplier/product/location from corrected chemistry hardware provider; nocompletepack or extra centralBMS input. Update freight pernewmodulemanufacturedmass using existingonekg-route intensities,while currentnoncell hardware references remainfixed. Cell manufacture energy is includedupstream,not chargedagain. Original288kgsourcewholeHSS mass and140/190Wh/kgmetadata are historical,not the updatedengineeringvariant; complete noncell component retainedmass/yields are not certified by newmodule closure. ModulebaselineLFP149.6736kg,NMC129.316457142857kg excludesother unchangedHSSperiphery. No source systemlifetime,operatingloss,DoD orreplacement change here; issues66/67 reconcilethose separately. This fixedhomecell-design path does not silently inheritmobile futuredensitylearning. Existing legacykgmoduleprovidersremainavailable forother consumers. No native/runtime edits or recyclingcredits; omitteddevice-specificEOL remains explicitgap. Currentreference:chemistryLFP,nominal14.4kWh,cell specific energy160.0Wh/kg,installedcellmass90.0kg,modulenoncellmass59.6736kg,totalmodulemass149.6736kg.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -1839,53 +1840,229 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="1" t="s">
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>-90.0</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kilogram</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GLO</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">technosphere</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">End-of-life cells; lifetime-manufactured finished-component mass, counted once. Existing market mix and geography are treatment proxies; no additional recovery credit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market for used industrial electronic device</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">used industrial electronic device</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>-56.2464</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kilogram</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RoW</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">technosphere</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">End-of-life electronics; lifetime-manufactured finished-component mass, counted once. Existing market mix and geography are treatment proxies; no additional recovery credit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market for waste electric wiring</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waste electric wiring</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>-9.936</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kilogram</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RoW</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">technosphere</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">End-of-life cables; lifetime-manufactured finished-component mass, counted once. Existing market mix and geography are treatment proxies; no additional recovery credit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market for waste bulk iron, excluding reinforcement</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waste bulk iron, excluding reinforcement</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>-138.10464</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kilogram</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RoW</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">technosphere</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">End-of-life steel; lifetime-manufactured finished-component mass, counted once. Existing market mix and geography are treatment proxies; no additional recovery credit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market for waste rubber, unspecified</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waste rubber, unspecified</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.25056</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kilogram</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RoW</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">technosphere</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">End-of-life rubber; lifetime-manufactured finished-component mass, counted once. Existing market mix and geography are treatment proxies; no additional recovery credit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>1</v>
-      </c>
-      <c r="B49" t="s">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>1</v>
+      </c>
+      <c r="B54" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
         <v>4</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B55" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
         <v>2</v>
       </c>
-      <c r="B51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
+      <c r="B56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
         <v>3</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B57" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
         <v>7</v>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>APPROVED HOME-STORAGE COMPONENT LIFE BUDGETS, issue67,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899 Table3,minimum/maximum calendar and cyclelife. Recompute for retained13years/2500cycles,NOT copy published20year/7300cycle factors. For eachcomponent selecthigh/lowmanufacturedsets=max(1,systemyears/componentyears,systemcycles/componentcycles),usingpairedlow/highlife endpoints,then midpointsets as engineeringexpectedlifetimeattribution. Clampatonebecauseanewcompleteinstalledsetisrequired; no assumedreusecredit for residualcomponentlife. This is not a probabilisticfailure distribution or literal fractionalinstallation. ReferenceLFPcellsets1,NMC811cellsets1.125;charger/inverter/controls/moduleBMSsets1.3125;cables1.15;housing/module steel1.0. Sourcepublished1.96/2.43cell and1.92electronics factors refer20years/7300cycles andmustnot be blindly transferred. Each home system activity now means an installeddesignplusits13yearmanufacturingreplacementbudget; labelsnominalkWhstayinstalledcapacity,not manufacturedcapacitysum. Multiplycellmanufactureonly bycellfactor within newunitmodule; moduleBMS follows electronicsfactor,modulesteel/rolling remainoneinstalledset. Externalsteelhousingremainsone,externalcontroller/electronics,charger,inverter andcablesfollowtheir own factors. Do not multiplythewholemodule anditscellsagain or buyanotherfullhome systemfor inverterfailure. Increasecomponentfreight withactualmanufacturedcomponentmass; retaininitialassemblyelectricityonce because source replacementassemblyenergy is unspecified,which remains a coveragegap. Existing servicewrapperstays1/consumerlifetimekWh fromissue66; operatingelectricity,DoD,nominalinstalledcapacity andcalendarhorizonunchanged. Transportation is at original routeintensities; packaging/maintenance labour and returntransport are gaps. Device-specific treatment/recycling is not invented; no recoverycredits orprimarysecondaryshares added. Future electronicsdurability is a sourceassumption,not verifiedmodernfleetlife. Sensitivityuseslistedmin/maxsets andsourcecalendar/cyclelimits. Numericreference:{"LFP":{"min_sets":1,"max_sets":1,"reference_sets":1.0},"NMC811":{"min_sets":1,"max_sets":1.25,"reference_sets":1.125},"electronics":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"inverter":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"charger":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"cable":{"min_sets":1,"max_sets":1.3,"reference_sets":1.15},"housing":{"min_sets":1,"max_sets":1,"reference_sets":1.0}}
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HOME-STORAGE END-OF-LIFE COVERAGE, 2026-10-19. Add terminal treatment at this complete-system lifetime-budget level only. Finished cells 78.3482142857143 kg; charger, inverter, controller, separate control electronics and module BMS 56.2464 kg; cables 9.936 kg; structural steel 138.10464 kg; housing rubber 0.25056 kg. Total 282.885814285714 kg matches lifetime manufactured finished components. Existing replacement factors are already included in these purchases; do not apply them again. Housing is split using its existing 99.7% steel/0.3% rubber recipe; module steel is separate. Electronics are routed as finished devices, not counted again as constituent metals. Cells retain the existing generic Li-ion waste-market proxy; electronics, wiring, bulk iron and rubber use their existing waste treatment markets. These are documented treatment/geography proxies (GLO battery; RoW other waste markets) for the RER home system, not device-specific measured recovery yields or a Swiss disposal mix. Native market treatment/recovery conventions are retained without adding independent material substitution credits or new primary/secondary assumptions. Negative kg technosphere amounts send discarded products to waste markets whose reference production is -1 kg. Manufacturing process services/losses are not added to retained final-product waste. All lifetime-manufactured components are assigned eventual treatment in this attributional lifecycle reference; timing, reuse and remaining life are not dynamically modelled. Existing operational energy, nominal capacity, manufacturing, replacement factors and lifetime output remain unchanged. No additional whole-battery-capacity purchase or disassembly/EOL helper is added upstream. The following historical omission notes are superseded by this explicit treatment addition.
+APPROVED HOME-STORAGE COMPONENT LIFE BUDGETS, issue67,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899 Table3,minimum/maximum calendar and cyclelife. Recompute for retained13years/2500cycles,NOT copy published20year/7300cycle factors. For eachcomponent selecthigh/lowmanufacturedsets=max(1,systemyears/componentyears,systemcycles/componentcycles),usingpairedlow/highlife endpoints,then midpointsets as engineeringexpectedlifetimeattribution. Clampatonebecauseanewcompleteinstalledsetisrequired; no assumedreusecredit for residualcomponentlife. This is not a probabilisticfailure distribution or literal fractionalinstallation. ReferenceLFPcellsets1,NMC811cellsets1.125;charger/inverter/controls/moduleBMSsets1.3125;cables1.15;housing/module steel1.0. Sourcepublished1.96/2.43cell and1.92electronics factors refer20years/7300cycles andmustnot be blindly transferred. Each home system activity now means an installeddesignplusits13yearmanufacturingreplacementbudget; labelsnominalkWhstayinstalledcapacity,not manufacturedcapacitysum. Multiplycellmanufactureonly bycellfactor within newunitmodule; moduleBMS follows electronicsfactor,modulesteel/rolling remainoneinstalledset. Externalsteelhousingremainsone,externalcontroller/electronics,charger,inverter andcablesfollowtheir own factors. Do not multiplythewholemodule anditscellsagain or buyanotherfullhome systemfor inverterfailure. Increasecomponentfreight withactualmanufacturedcomponentmass; retaininitialassemblyelectricityonce because source replacementassemblyenergy is unspecified,which remains a coveragegap. Existing servicewrapperstays1/consumerlifetimekWh fromissue66; operatingelectricity,DoD,nominalinstalledcapacity andcalendarhorizonunchanged. Transportation is at original routeintensities; packaging/maintenance labour and returntransport are gaps. Device-specific treatment/recycling is not invented; no recoverycredits orprimarysecondaryshares added. Future electronicsdurability is a sourceassumption,not verifiedmodernfleetlife. Sensitivityuseslistedmin/maxsets andsourcecalendar/cyclelimits. Numericreference:{"LFP":{"min_sets":1,"max_sets":1,"reference_sets":1.0},"NMC811":{"min_sets":1,"max_sets":1.25,"reference_sets":1.125},"electronics":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"inverter":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"charger":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"cable":{"min_sets":1,"max_sets":1.3,"reference_sets":1.15},"housing":{"min_sets":1,"max_sets":1,"reference_sets":1.0}}
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED HOME-STORAGE CELL/CAPACITY RECONCILIATION, issue65,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells. Retain labelled14.4kWhLFP and19.5kWhNMC811 grossnominalcapacity. Previous161.28kgmodule*0.63=101.6064kgcells produces14.224896/19.305216kWh even at copied140/190Wh/kg,and the actually linkedgenericcell reference is different again. Adopt the already accepted chemistry-specific160/280Wh/kg reference,so manufacture90kgLFPcells or69.642857142857kgNMC811cells per installedhome system. This selects a coherent currentcell-reference variant; it is NOT evidence original sourcecapacity or measuredcellmass were wrong. Source-specific Mohr cell inventories and precise pouch geometry remain a comparison gap. Preserve54.8352kgmodule steel,4.8384kg moduleBMS and their existingmanufacturing/transport proxies as fixed engineeringhousing architecture; do not fill releasedcellmass with arbitrarymetal tohold161.28kg. New moduleprovider is oneunit for allinstalledmodules in onehome system,not onekg or onephysicalcell. Retain exactcell supplier/product/location from corrected chemistry hardware provider; nocompletepack or extra centralBMS input. Update freight pernewmodulemanufacturedmass using existingonekg-route intensities,while currentnoncell hardware references remainfixed. Cell manufacture energy is includedupstream,not chargedagain. Original288kgsourcewholeHSS mass and140/190Wh/kgmetadata are historical,not the updatedengineeringvariant; complete noncell component retainedmass/yields are not certified by newmodule closure. ModulebaselineLFP149.6736kg,NMC129.316457142857kg excludesother unchangedHSSperiphery. No source systemlifetime,operatingloss,DoD orreplacement change here; issues66/67 reconcilethose separately. This fixedhomecell-design path does not silently inheritmobile futuredensitylearning. Existing legacykgmoduleprovidersremainavailable forother consumers. No native/runtime edits or recyclingcredits; omitteddevice-specificEOL remains explicitgap. Currentreference:chemistryNMC811,nominal19.5kWh,cell specific energy280.0Wh/kg,installedcellmass69.64285714285714kg,modulenoncellmass59.6736kg,totalmodulemass129.31645714285713kg.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -1901,182 +2078,67 @@
         </is>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A56" t="str">
-        <f>B48</f>
-        <v>home electricity storage system, 19.5 kWh, NMC811 battery</v>
-      </c>
-      <c r="B56" t="str">
-        <f>B49</f>
-        <v>home electricity storage system</v>
-      </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-      <c r="D56" t="str">
-        <f>B52</f>
-        <v>unit</v>
-      </c>
-      <c r="E56" t="str">
-        <f>B50</f>
-        <v>RER</v>
-      </c>
-      <c r="F56" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>85</v>
-      </c>
-      <c r="B57" t="s">
-        <v>86</v>
-      </c>
-      <c r="C57">
-        <v>18.900000000000002</v>
-      </c>
-      <c r="D57" t="s">
-        <v>76</v>
-      </c>
-      <c r="E57" t="s">
-        <v>16</v>
-      </c>
-      <c r="F57" t="s">
-        <v>89</v>
-      </c>
-      <c r="G57" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>81</v>
-      </c>
-      <c r="B58" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58">
-        <v>9.936</v>
-      </c>
-      <c r="D58" t="s">
-        <v>76</v>
-      </c>
-      <c r="E58" t="s">
-        <v>14</v>
-      </c>
-      <c r="F58" t="s">
-        <v>89</v>
-      </c>
-      <c r="G58" t="s">
-        <v>18</v>
-      </c>
-    </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>82</v>
-      </c>
-      <c r="B59" t="s">
-        <v>11</v>
-      </c>
-      <c r="C59">
-        <v>34.56</v>
-      </c>
-      <c r="D59" t="s">
-        <v>77</v>
-      </c>
-      <c r="E59" t="s">
-        <v>15</v>
-      </c>
-      <c r="F59" t="s">
-        <v>89</v>
-      </c>
-      <c r="G59" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>83</v>
-      </c>
-      <c r="B60" t="s">
-        <v>12</v>
-      </c>
-      <c r="C60">
-        <v>0.7560000000000001</v>
-      </c>
-      <c r="D60" t="s">
-        <v>76</v>
-      </c>
-      <c r="E60" t="s">
-        <v>14</v>
-      </c>
-      <c r="F60" t="s">
-        <v>89</v>
-      </c>
-      <c r="G60" t="s">
-        <v>20</v>
+      <c r="A60" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>109</v>
-      </c>
-      <c r="B61" t="s">
-        <v>87</v>
+      <c r="A61" t="str">
+        <f>B53</f>
+        <v>home electricity storage system, 19.5 kWh, NMC811 battery</v>
+      </c>
+      <c r="B61" t="str">
+        <f>B54</f>
+        <v>home electricity storage system</v>
       </c>
       <c r="C61">
-        <v>83.52</v>
-      </c>
-      <c r="D61" t="s">
-        <v>76</v>
-      </c>
-      <c r="E61" t="s">
-        <v>16</v>
+        <v>1</v>
+      </c>
+      <c r="D61" t="str">
+        <f>B57</f>
+        <v>unit</v>
+      </c>
+      <c r="E61" t="str">
+        <f>B55</f>
+        <v>RER</v>
       </c>
       <c r="F61" t="s">
-        <v>89</v>
-      </c>
-      <c r="G61" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="B62" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C62">
-        <v>22.68</v>
+        <v>18.900000000000002</v>
       </c>
       <c r="D62" t="s">
         <v>76</v>
@@ -2088,428 +2150,488 @@
         <v>89</v>
       </c>
       <c r="G62" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery module production, home storage, Li-ion, NMC811, 19.5 kWh</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery module, home storage, Li-ion, NMC811, 19.5 kWh</t>
-        </is>
+      <c r="A63" t="s">
+        <v>81</v>
+      </c>
+      <c r="B63" t="s">
+        <v>10</v>
       </c>
       <c r="C63">
-        <v>1</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
+        <v>9.936</v>
+      </c>
+      <c r="D63" t="s">
+        <v>76</v>
+      </c>
+      <c r="E63" t="s">
+        <v>14</v>
       </c>
       <c r="F63" t="s">
         <v>89</v>
       </c>
       <c r="G63" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="B64" t="s">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="C64">
-        <v>7.56</v>
+        <v>34.56</v>
       </c>
       <c r="D64" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F64" t="s">
         <v>89</v>
       </c>
       <c r="G64" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C65">
-        <v>90.3528</v>
+        <v>0.7560000000000001</v>
       </c>
       <c r="D65" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E65" t="s">
+        <v>14</v>
+      </c>
+      <c r="F65" t="s">
+        <v>89</v>
+      </c>
+      <c r="G65" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>109</v>
+      </c>
+      <c r="B66" t="s">
+        <v>87</v>
+      </c>
+      <c r="C66">
+        <v>83.52</v>
+      </c>
+      <c r="D66" t="s">
+        <v>76</v>
+      </c>
+      <c r="E66" t="s">
         <v>16</v>
       </c>
-      <c r="F65" t="s">
-        <v>89</v>
-      </c>
-      <c r="G65" t="s">
-        <v>25</v>
+      <c r="F66" t="s">
+        <v>89</v>
+      </c>
+      <c r="G66" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A67" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>85</v>
+      <c r="A67" t="s">
+        <v>111</v>
+      </c>
+      <c r="B67" t="s">
+        <v>88</v>
+      </c>
+      <c r="C67">
+        <v>22.68</v>
+      </c>
+      <c r="D67" t="s">
+        <v>76</v>
+      </c>
+      <c r="E67" t="s">
+        <v>16</v>
+      </c>
+      <c r="F67" t="s">
+        <v>89</v>
+      </c>
+      <c r="G67" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>1</v>
-      </c>
-      <c r="B68" t="s">
-        <v>86</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">battery module production, home storage, Li-ion, NMC811, 19.5 kWh</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">battery module, home storage, Li-ion, NMC811, 19.5 kWh</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="F68" t="s">
+        <v>89</v>
+      </c>
+      <c r="G68" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>4</v>
+        <v>119</v>
       </c>
       <c r="B69" t="s">
+        <v>120</v>
+      </c>
+      <c r="C69">
+        <v>7.56</v>
+      </c>
+      <c r="D69" t="s">
+        <v>76</v>
+      </c>
+      <c r="E69" t="s">
         <v>16</v>
+      </c>
+      <c r="F69" t="s">
+        <v>89</v>
+      </c>
+      <c r="G69" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>2</v>
-      </c>
-      <c r="B70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>3</v>
-      </c>
-      <c r="B71" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>7</v>
-      </c>
-      <c r="B72" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A75" t="str">
-        <f>B67</f>
-        <v>ampere charger production</v>
-      </c>
-      <c r="B75" t="str">
-        <f>B68</f>
-        <v>ampere charger for home storage system</v>
-      </c>
-      <c r="C75">
-        <v>1</v>
-      </c>
-      <c r="D75" t="str">
-        <f>B71</f>
-        <v>kilogram</v>
-      </c>
-      <c r="E75" t="str">
-        <f>B69</f>
-        <v>RER</v>
-      </c>
-      <c r="F75" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>90</v>
-      </c>
-      <c r="B76" t="s">
-        <v>26</v>
-      </c>
-      <c r="C76" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="D76" t="s">
-        <v>76</v>
-      </c>
-      <c r="E76" t="s">
-        <v>14</v>
-      </c>
-      <c r="F76" t="s">
-        <v>89</v>
-      </c>
-      <c r="G76" t="s">
-        <v>38</v>
+        <v>84</v>
+      </c>
+      <c r="B70" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70">
+        <v>90.3528</v>
+      </c>
+      <c r="D70" t="s">
+        <v>78</v>
+      </c>
+      <c r="E70" t="s">
+        <v>16</v>
+      </c>
+      <c r="F70" t="s">
+        <v>89</v>
+      </c>
+      <c r="G70" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>-78.34821428571428</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kilogram</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GLO</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">technosphere</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">End-of-life cells; lifetime-manufactured finished-component mass, counted once. Existing market mix and geography are treatment proxies; no additional recovery credit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market for used industrial electronic device</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">used industrial electronic device</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>-56.2464</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kilogram</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RoW</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">technosphere</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">End-of-life electronics; lifetime-manufactured finished-component mass, counted once. Existing market mix and geography are treatment proxies; no additional recovery credit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market for waste electric wiring</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waste electric wiring</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>-9.936</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kilogram</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RoW</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">technosphere</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">End-of-life cables; lifetime-manufactured finished-component mass, counted once. Existing market mix and geography are treatment proxies; no additional recovery credit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market for waste bulk iron, excluding reinforcement</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waste bulk iron, excluding reinforcement</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>-138.10464</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kilogram</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RoW</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">technosphere</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">End-of-life steel; lifetime-manufactured finished-component mass, counted once. Existing market mix and geography are treatment proxies; no additional recovery credit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market for waste rubber, unspecified</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waste rubber, unspecified</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.25056</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kilogram</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RoW</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">technosphere</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">End-of-life rubber; lifetime-manufactured finished-component mass, counted once. Existing market mix and geography are treatment proxies; no additional recovery credit.</t>
+        </is>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>81</v>
-      </c>
-      <c r="B77" t="s">
-        <v>10</v>
-      </c>
-      <c r="C77" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="D77" t="s">
-        <v>76</v>
-      </c>
-      <c r="E77" t="s">
-        <v>14</v>
-      </c>
-      <c r="F77" t="s">
-        <v>89</v>
-      </c>
-      <c r="G77" t="s">
-        <v>18</v>
+      <c r="A77" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="B78" t="s">
-        <v>27</v>
-      </c>
-      <c r="C78" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="D78" t="s">
-        <v>76</v>
-      </c>
-      <c r="E78" t="s">
-        <v>14</v>
-      </c>
-      <c r="F78" t="s">
-        <v>89</v>
-      </c>
-      <c r="G78" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>92</v>
+        <v>4</v>
       </c>
       <c r="B79" t="s">
-        <v>28</v>
-      </c>
-      <c r="C79" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="D79" t="s">
-        <v>76</v>
-      </c>
-      <c r="E79" t="s">
-        <v>14</v>
-      </c>
-      <c r="F79" t="s">
-        <v>89</v>
-      </c>
-      <c r="G79" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>93</v>
-      </c>
-      <c r="B80" t="s">
-        <v>29</v>
-      </c>
-      <c r="C80" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="D80" t="s">
-        <v>76</v>
-      </c>
-      <c r="E80" t="s">
-        <v>14</v>
-      </c>
-      <c r="F80" t="s">
-        <v>89</v>
-      </c>
-      <c r="G80" t="s">
-        <v>41</v>
+        <v>2</v>
+      </c>
+      <c r="B80">
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>94</v>
+        <v>3</v>
       </c>
       <c r="B81" t="s">
-        <v>30</v>
-      </c>
-      <c r="C81" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="D81" t="s">
-        <v>76</v>
-      </c>
-      <c r="E81" t="s">
-        <v>14</v>
-      </c>
-      <c r="F81" t="s">
-        <v>89</v>
-      </c>
-      <c r="G81" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B82" t="s">
-        <v>104</v>
-      </c>
-      <c r="C82">
-        <v>0.08</v>
-      </c>
-      <c r="D82" t="s">
-        <v>76</v>
-      </c>
-      <c r="E82" t="s">
-        <v>16</v>
-      </c>
-      <c r="F82" t="s">
-        <v>89</v>
-      </c>
-      <c r="G82" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>95</v>
-      </c>
-      <c r="B83" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D83" t="s">
-        <v>76</v>
-      </c>
-      <c r="E83" t="s">
-        <v>14</v>
-      </c>
-      <c r="F83" t="s">
-        <v>89</v>
-      </c>
-      <c r="G83" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>96</v>
-      </c>
-      <c r="B84" t="s">
-        <v>32</v>
-      </c>
-      <c r="C84">
-        <v>0.15</v>
-      </c>
-      <c r="D84" t="s">
-        <v>76</v>
-      </c>
-      <c r="E84" t="s">
-        <v>14</v>
-      </c>
-      <c r="F84" t="s">
-        <v>89</v>
-      </c>
-      <c r="G84" t="s">
-        <v>45</v>
+      <c r="A84" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
-        <v>97</v>
-      </c>
-      <c r="B85" t="s">
-        <v>33</v>
+      <c r="A85" t="str">
+        <f>B77</f>
+        <v>ampere charger production</v>
+      </c>
+      <c r="B85" t="str">
+        <f>B78</f>
+        <v>ampere charger for home storage system</v>
       </c>
       <c r="C85">
-        <v>0.51</v>
-      </c>
-      <c r="D85" t="s">
-        <v>76</v>
-      </c>
-      <c r="E85" t="s">
-        <v>14</v>
+        <v>1</v>
+      </c>
+      <c r="D85" t="str">
+        <f>B81</f>
+        <v>kilogram</v>
+      </c>
+      <c r="E85" t="str">
+        <f>B79</f>
+        <v>RER</v>
       </c>
       <c r="F85" t="s">
-        <v>89</v>
-      </c>
-      <c r="G85" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B86" t="s">
-        <v>34</v>
-      </c>
-      <c r="C86">
-        <v>0.02</v>
+        <v>26</v>
+      </c>
+      <c r="C86" s="2">
+        <v>0.15</v>
       </c>
       <c r="D86" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E86" t="s">
         <v>14</v>
@@ -2518,18 +2640,18 @@
         <v>89</v>
       </c>
       <c r="G86" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="B87" t="s">
-        <v>35</v>
-      </c>
-      <c r="C87">
-        <v>0.51</v>
+        <v>10</v>
+      </c>
+      <c r="C87" s="2">
+        <v>0.02</v>
       </c>
       <c r="D87" t="s">
         <v>76</v>
@@ -2541,67 +2663,67 @@
         <v>89</v>
       </c>
       <c r="G87" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>36</v>
-      </c>
-      <c r="C88">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="C88" s="2">
+        <v>0.01</v>
       </c>
       <c r="D88" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E88" t="s">
-        <v>116</v>
+        <v>14</v>
       </c>
       <c r="F88" t="s">
         <v>89</v>
       </c>
       <c r="G88" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B89" t="s">
-        <v>13</v>
-      </c>
-      <c r="C89">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="C89" s="2">
+        <v>0.01</v>
       </c>
       <c r="D89" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E89" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F89" t="s">
         <v>89</v>
       </c>
       <c r="G89" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>37</v>
-      </c>
-      <c r="C90">
-        <v>8</v>
+        <v>29</v>
+      </c>
+      <c r="C90" s="2">
+        <v>0.01</v>
       </c>
       <c r="D90" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E90" t="s">
         <v>14</v>
@@ -2610,798 +2732,801 @@
         <v>89</v>
       </c>
       <c r="G90" t="s">
-        <v>51</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>94</v>
+      </c>
+      <c r="B91" t="s">
+        <v>30</v>
+      </c>
+      <c r="C91" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="D91" t="s">
+        <v>76</v>
+      </c>
+      <c r="E91" t="s">
+        <v>14</v>
+      </c>
+      <c r="F91" t="s">
+        <v>89</v>
+      </c>
+      <c r="G91" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A92" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B92" s="1" t="s">
+      <c r="A92" t="s">
         <v>103</v>
+      </c>
+      <c r="B92" t="s">
+        <v>104</v>
+      </c>
+      <c r="C92">
+        <v>0.08</v>
+      </c>
+      <c r="D92" t="s">
+        <v>76</v>
+      </c>
+      <c r="E92" t="s">
+        <v>16</v>
+      </c>
+      <c r="F92" t="s">
+        <v>89</v>
+      </c>
+      <c r="G92" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="B93" t="s">
-        <v>104</v>
+        <v>31</v>
+      </c>
+      <c r="C93">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D93" t="s">
+        <v>76</v>
+      </c>
+      <c r="E93" t="s">
+        <v>14</v>
+      </c>
+      <c r="F93" t="s">
+        <v>89</v>
+      </c>
+      <c r="G93" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="B94" t="s">
-        <v>16</v>
+        <v>32</v>
+      </c>
+      <c r="C94">
+        <v>0.15</v>
+      </c>
+      <c r="D94" t="s">
+        <v>76</v>
+      </c>
+      <c r="E94" t="s">
+        <v>14</v>
+      </c>
+      <c r="F94" t="s">
+        <v>89</v>
+      </c>
+      <c r="G94" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>2</v>
-      </c>
-      <c r="B95">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="B95" t="s">
+        <v>33</v>
+      </c>
+      <c r="C95">
+        <v>0.51</v>
+      </c>
+      <c r="D95" t="s">
+        <v>76</v>
+      </c>
+      <c r="E95" t="s">
+        <v>14</v>
+      </c>
+      <c r="F95" t="s">
+        <v>89</v>
+      </c>
+      <c r="G95" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="B96" t="s">
-        <v>76</v>
+        <v>34</v>
+      </c>
+      <c r="C96">
+        <v>0.02</v>
+      </c>
+      <c r="D96" t="s">
+        <v>79</v>
+      </c>
+      <c r="E96" t="s">
+        <v>14</v>
+      </c>
+      <c r="F96" t="s">
+        <v>89</v>
+      </c>
+      <c r="G96" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="B97" t="s">
-        <v>75</v>
+        <v>35</v>
+      </c>
+      <c r="C97">
+        <v>0.51</v>
+      </c>
+      <c r="D97" t="s">
+        <v>76</v>
+      </c>
+      <c r="E97" t="s">
+        <v>14</v>
+      </c>
+      <c r="F97" t="s">
+        <v>89</v>
+      </c>
+      <c r="G97" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>9</v>
+        <v>100</v>
+      </c>
+      <c r="B98" t="s">
+        <v>36</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98" t="s">
+        <v>78</v>
+      </c>
+      <c r="E98" t="s">
+        <v>116</v>
+      </c>
+      <c r="F98" t="s">
+        <v>89</v>
+      </c>
+      <c r="G98" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="B99" t="s">
-        <v>1</v>
-      </c>
-      <c r="C99" t="s">
-        <v>2</v>
+        <v>13</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
       </c>
       <c r="D99" t="s">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="E99" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F99" t="s">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="G99" t="s">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A100" t="str">
-        <f>B92</f>
-        <v>inductor, other production</v>
-      </c>
-      <c r="B100" t="str">
-        <f>B93</f>
-        <v>inductor, other</v>
+      <c r="A100" t="s">
+        <v>101</v>
+      </c>
+      <c r="B100" t="s">
+        <v>37</v>
       </c>
       <c r="C100">
-        <v>1</v>
-      </c>
-      <c r="D100" t="str">
-        <f>B96</f>
-        <v>kilogram</v>
-      </c>
-      <c r="E100" t="str">
-        <f>B94</f>
-        <v>RER</v>
+        <v>8</v>
+      </c>
+      <c r="D100" t="s">
+        <v>78</v>
+      </c>
+      <c r="E100" t="s">
+        <v>14</v>
       </c>
       <c r="F100" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>105</v>
-      </c>
-      <c r="B101" t="s">
-        <v>52</v>
-      </c>
-      <c r="C101">
-        <v>0.46</v>
-      </c>
-      <c r="D101" t="s">
-        <v>76</v>
-      </c>
-      <c r="E101" t="s">
-        <v>14</v>
-      </c>
-      <c r="F101" t="s">
-        <v>89</v>
-      </c>
-      <c r="G101" t="s">
-        <v>56</v>
+        <v>89</v>
+      </c>
+      <c r="G100" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
-        <v>106</v>
-      </c>
-      <c r="B102" t="s">
-        <v>53</v>
-      </c>
-      <c r="C102">
-        <v>0.43</v>
-      </c>
-      <c r="D102" t="s">
-        <v>76</v>
-      </c>
-      <c r="E102" t="s">
-        <v>14</v>
-      </c>
-      <c r="F102" t="s">
-        <v>89</v>
-      </c>
-      <c r="G102" t="s">
-        <v>57</v>
+      <c r="A102" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="B103" t="s">
-        <v>29</v>
-      </c>
-      <c r="C103">
-        <v>0.04</v>
-      </c>
-      <c r="D103" t="s">
-        <v>76</v>
-      </c>
-      <c r="E103" t="s">
-        <v>14</v>
-      </c>
-      <c r="F103" t="s">
-        <v>89</v>
-      </c>
-      <c r="G103" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
       <c r="B104" t="s">
-        <v>54</v>
-      </c>
-      <c r="C104">
-        <v>1</v>
-      </c>
-      <c r="D104" t="s">
-        <v>76</v>
-      </c>
-      <c r="E104" t="s">
-        <v>14</v>
-      </c>
-      <c r="F104" t="s">
-        <v>89</v>
-      </c>
-      <c r="G104" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>99</v>
-      </c>
-      <c r="B105" t="s">
-        <v>35</v>
-      </c>
-      <c r="C105">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="D105" t="s">
-        <v>76</v>
-      </c>
-      <c r="E105" t="s">
-        <v>14</v>
-      </c>
-      <c r="F105" t="s">
-        <v>89</v>
-      </c>
-      <c r="G105" t="s">
-        <v>48</v>
+        <v>2</v>
+      </c>
+      <c r="B105">
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>108</v>
+        <v>3</v>
       </c>
       <c r="B106" t="s">
-        <v>55</v>
-      </c>
-      <c r="C106">
-        <v>0.43</v>
-      </c>
-      <c r="D106" t="s">
-        <v>76</v>
-      </c>
-      <c r="E106" t="s">
-        <v>14</v>
-      </c>
-      <c r="F106" t="s">
-        <v>89</v>
-      </c>
-      <c r="G106" t="s">
-        <v>60</v>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>7</v>
+      </c>
+      <c r="B107" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A108" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>109</v>
+      <c r="A108" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>87</v>
+        <v>1</v>
+      </c>
+      <c r="C109" t="s">
+        <v>2</v>
+      </c>
+      <c r="D109" t="s">
+        <v>3</v>
+      </c>
+      <c r="E109" t="s">
+        <v>4</v>
+      </c>
+      <c r="F109" t="s">
+        <v>6</v>
+      </c>
+      <c r="G109" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
-        <v>4</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
+      <c r="A110" t="str">
+        <f>B102</f>
+        <v>inductor, other production</v>
+      </c>
+      <c r="B110" t="str">
+        <f>B103</f>
+        <v>inductor, other</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+      <c r="D110" t="str">
+        <f>B106</f>
+        <v>kilogram</v>
+      </c>
+      <c r="E110" t="str">
+        <f>B104</f>
+        <v>RER</v>
+      </c>
+      <c r="F110" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>2</v>
-      </c>
-      <c r="B111">
-        <v>1</v>
+        <v>105</v>
+      </c>
+      <c r="B111" t="s">
+        <v>52</v>
+      </c>
+      <c r="C111">
+        <v>0.46</v>
+      </c>
+      <c r="D111" t="s">
+        <v>76</v>
+      </c>
+      <c r="E111" t="s">
+        <v>14</v>
+      </c>
+      <c r="F111" t="s">
+        <v>89</v>
+      </c>
+      <c r="G111" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="B112" t="s">
-        <v>76</v>
+        <v>53</v>
+      </c>
+      <c r="C112">
+        <v>0.43</v>
+      </c>
+      <c r="D112" t="s">
+        <v>76</v>
+      </c>
+      <c r="E112" t="s">
+        <v>14</v>
+      </c>
+      <c r="F112" t="s">
+        <v>89</v>
+      </c>
+      <c r="G112" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>7</v>
+        <v>93</v>
       </c>
       <c r="B113" t="s">
-        <v>75</v>
+        <v>29</v>
+      </c>
+      <c r="C113">
+        <v>0.04</v>
+      </c>
+      <c r="D113" t="s">
+        <v>76</v>
+      </c>
+      <c r="E113" t="s">
+        <v>14</v>
+      </c>
+      <c r="F113" t="s">
+        <v>89</v>
+      </c>
+      <c r="G113" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>9</v>
+        <v>107</v>
+      </c>
+      <c r="B114" t="s">
+        <v>54</v>
+      </c>
+      <c r="C114">
+        <v>1</v>
+      </c>
+      <c r="D114" t="s">
+        <v>76</v>
+      </c>
+      <c r="E114" t="s">
+        <v>14</v>
+      </c>
+      <c r="F114" t="s">
+        <v>89</v>
+      </c>
+      <c r="G114" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A115" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>7</v>
+      <c r="A115" t="s">
+        <v>99</v>
+      </c>
+      <c r="B115" t="s">
+        <v>35</v>
+      </c>
+      <c r="C115">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D115" t="s">
+        <v>76</v>
+      </c>
+      <c r="E115" t="s">
+        <v>14</v>
+      </c>
+      <c r="F115" t="s">
+        <v>89</v>
+      </c>
+      <c r="G115" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A116" t="str">
-        <f>B108</f>
-        <v>housing assembly for home storage system</v>
-      </c>
-      <c r="B116" t="str">
-        <f>B109</f>
-        <v>housing for home storage system</v>
+      <c r="A116" t="s">
+        <v>108</v>
+      </c>
+      <c r="B116" t="s">
+        <v>55</v>
       </c>
       <c r="C116">
-        <v>1</v>
-      </c>
-      <c r="D116" t="str">
-        <f>B112</f>
-        <v>kilogram</v>
-      </c>
-      <c r="E116" t="str">
-        <f>B110</f>
-        <v>RER</v>
+        <v>0.43</v>
+      </c>
+      <c r="D116" t="s">
+        <v>76</v>
+      </c>
+      <c r="E116" t="s">
+        <v>14</v>
       </c>
       <c r="F116" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A117" t="s">
-        <v>97</v>
-      </c>
-      <c r="B117" t="s">
-        <v>33</v>
-      </c>
-      <c r="C117">
-        <v>0.997</v>
-      </c>
-      <c r="D117" t="s">
-        <v>76</v>
-      </c>
-      <c r="E117" t="s">
-        <v>14</v>
-      </c>
-      <c r="F117" t="s">
-        <v>89</v>
-      </c>
-      <c r="G117" t="s">
-        <v>46</v>
+        <v>89</v>
+      </c>
+      <c r="G116" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A118" t="s">
-        <v>99</v>
-      </c>
-      <c r="B118" t="s">
-        <v>35</v>
-      </c>
-      <c r="C118">
-        <v>0.997</v>
-      </c>
-      <c r="D118" t="s">
-        <v>76</v>
-      </c>
-      <c r="E118" t="s">
-        <v>14</v>
-      </c>
-      <c r="F118" t="s">
-        <v>89</v>
-      </c>
-      <c r="G118" t="s">
-        <v>48</v>
+      <c r="A118" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="B119" t="s">
-        <v>61</v>
-      </c>
-      <c r="C119">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="D119" t="s">
-        <v>76</v>
-      </c>
-      <c r="E119" t="s">
-        <v>14</v>
-      </c>
-      <c r="F119" t="s">
-        <v>89</v>
-      </c>
-      <c r="G119" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="B120" t="s">
-        <v>36</v>
-      </c>
-      <c r="C120">
-        <v>0.2</v>
-      </c>
-      <c r="D120" t="s">
-        <v>78</v>
-      </c>
-      <c r="E120" t="s">
-        <v>116</v>
-      </c>
-      <c r="F120" t="s">
-        <v>89</v>
-      </c>
-      <c r="G120" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>84</v>
-      </c>
-      <c r="B121" t="s">
-        <v>13</v>
-      </c>
-      <c r="C121">
-        <v>0.1</v>
-      </c>
-      <c r="D121" t="s">
-        <v>78</v>
-      </c>
-      <c r="E121" t="s">
-        <v>16</v>
-      </c>
-      <c r="F121" t="s">
-        <v>89</v>
-      </c>
-      <c r="G121" t="s">
-        <v>63</v>
+        <v>2</v>
+      </c>
+      <c r="B121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>3</v>
+      </c>
+      <c r="B122" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A123" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>111</v>
+      <c r="A123" t="s">
+        <v>7</v>
+      </c>
+      <c r="B123" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>1</v>
-      </c>
-      <c r="B124" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A125" t="s">
+      <c r="A125" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E125" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B125" t="s">
-        <v>16</v>
+      <c r="F125" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A126" t="s">
-        <v>2</v>
-      </c>
-      <c r="B126">
-        <v>1</v>
+      <c r="A126" t="str">
+        <f>B118</f>
+        <v>housing assembly for home storage system</v>
+      </c>
+      <c r="B126" t="str">
+        <f>B119</f>
+        <v>housing for home storage system</v>
+      </c>
+      <c r="C126">
+        <v>1</v>
+      </c>
+      <c r="D126" t="str">
+        <f>B122</f>
+        <v>kilogram</v>
+      </c>
+      <c r="E126" t="str">
+        <f>B120</f>
+        <v>RER</v>
+      </c>
+      <c r="F126" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="B127" t="s">
-        <v>76</v>
+        <v>33</v>
+      </c>
+      <c r="C127">
+        <v>0.997</v>
+      </c>
+      <c r="D127" t="s">
+        <v>76</v>
+      </c>
+      <c r="E127" t="s">
+        <v>14</v>
+      </c>
+      <c r="F127" t="s">
+        <v>89</v>
+      </c>
+      <c r="G127" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="B128" t="s">
-        <v>75</v>
+        <v>35</v>
+      </c>
+      <c r="C128">
+        <v>0.997</v>
+      </c>
+      <c r="D128" t="s">
+        <v>76</v>
+      </c>
+      <c r="E128" t="s">
+        <v>14</v>
+      </c>
+      <c r="F128" t="s">
+        <v>89</v>
+      </c>
+      <c r="G128" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>9</v>
+        <v>110</v>
+      </c>
+      <c r="B129" t="s">
+        <v>61</v>
+      </c>
+      <c r="C129">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D129" t="s">
+        <v>76</v>
+      </c>
+      <c r="E129" t="s">
+        <v>14</v>
+      </c>
+      <c r="F129" t="s">
+        <v>89</v>
+      </c>
+      <c r="G129" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A130" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>7</v>
+      <c r="A130" t="s">
+        <v>100</v>
+      </c>
+      <c r="B130" t="s">
+        <v>36</v>
+      </c>
+      <c r="C130">
+        <v>0.2</v>
+      </c>
+      <c r="D130" t="s">
+        <v>78</v>
+      </c>
+      <c r="E130" t="s">
+        <v>116</v>
+      </c>
+      <c r="F130" t="s">
+        <v>89</v>
+      </c>
+      <c r="G130" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A131" t="str">
-        <f>B123</f>
-        <v>inverter production for home storage system</v>
-      </c>
-      <c r="B131" t="str">
-        <f>B124</f>
-        <v>inverter for home storage system</v>
+      <c r="A131" t="s">
+        <v>84</v>
+      </c>
+      <c r="B131" t="s">
+        <v>13</v>
       </c>
       <c r="C131">
-        <v>1</v>
-      </c>
-      <c r="D131" t="str">
-        <f>B127</f>
-        <v>kilogram</v>
-      </c>
-      <c r="E131" t="str">
-        <f>B125</f>
-        <v>RER</v>
+        <v>0.1</v>
+      </c>
+      <c r="D131" t="s">
+        <v>78</v>
+      </c>
+      <c r="E131" t="s">
+        <v>16</v>
       </c>
       <c r="F131" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A132" t="s">
-        <v>90</v>
-      </c>
-      <c r="B132" t="s">
-        <v>26</v>
-      </c>
-      <c r="C132">
-        <v>0.06</v>
-      </c>
-      <c r="D132" t="s">
-        <v>76</v>
-      </c>
-      <c r="E132" t="s">
-        <v>14</v>
-      </c>
-      <c r="F132" t="s">
-        <v>89</v>
-      </c>
-      <c r="G132" t="s">
-        <v>38</v>
+        <v>89</v>
+      </c>
+      <c r="G131" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A133" t="s">
-        <v>81</v>
-      </c>
-      <c r="B133" t="s">
-        <v>10</v>
-      </c>
-      <c r="C133">
-        <v>0.01</v>
-      </c>
-      <c r="D133" t="s">
-        <v>76</v>
-      </c>
-      <c r="E133" t="s">
-        <v>14</v>
-      </c>
-      <c r="F133" t="s">
-        <v>89</v>
-      </c>
-      <c r="G133" t="s">
-        <v>18</v>
+      <c r="A133" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="B134" t="s">
-        <v>27</v>
-      </c>
-      <c r="C134">
-        <v>0.03</v>
-      </c>
-      <c r="D134" t="s">
-        <v>76</v>
-      </c>
-      <c r="E134" t="s">
-        <v>14</v>
-      </c>
-      <c r="F134" t="s">
-        <v>89</v>
-      </c>
-      <c r="G134" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>92</v>
+        <v>4</v>
       </c>
       <c r="B135" t="s">
-        <v>28</v>
-      </c>
-      <c r="C135">
-        <v>0.04</v>
-      </c>
-      <c r="D135" t="s">
-        <v>76</v>
-      </c>
-      <c r="E135" t="s">
-        <v>14</v>
-      </c>
-      <c r="F135" t="s">
-        <v>89</v>
-      </c>
-      <c r="G135" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>94</v>
-      </c>
-      <c r="B136" t="s">
-        <v>30</v>
-      </c>
-      <c r="C136">
-        <v>0.01</v>
-      </c>
-      <c r="D136" t="s">
-        <v>76</v>
-      </c>
-      <c r="E136" t="s">
-        <v>14</v>
-      </c>
-      <c r="F136" t="s">
-        <v>89</v>
-      </c>
-      <c r="G136" t="s">
-        <v>42</v>
+        <v>2</v>
+      </c>
+      <c r="B136">
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="B137" t="s">
-        <v>104</v>
-      </c>
-      <c r="C137">
-        <v>0.27</v>
-      </c>
-      <c r="D137" t="s">
-        <v>76</v>
-      </c>
-      <c r="E137" t="s">
-        <v>16</v>
-      </c>
-      <c r="F137" t="s">
-        <v>89</v>
-      </c>
-      <c r="G137" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="B138" t="s">
-        <v>31</v>
-      </c>
-      <c r="C138">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="D138" t="s">
-        <v>76</v>
-      </c>
-      <c r="E138" t="s">
-        <v>14</v>
-      </c>
-      <c r="F138" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>96</v>
-      </c>
-      <c r="B139" t="s">
-        <v>32</v>
-      </c>
-      <c r="C139">
-        <v>0.05</v>
-      </c>
-      <c r="D139" t="s">
-        <v>76</v>
-      </c>
-      <c r="E139" t="s">
-        <v>14</v>
-      </c>
-      <c r="F139" t="s">
-        <v>89</v>
-      </c>
-      <c r="G139" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A140" t="s">
-        <v>97</v>
-      </c>
-      <c r="B140" t="s">
-        <v>33</v>
-      </c>
-      <c r="C140">
-        <v>0.45</v>
-      </c>
-      <c r="D140" t="s">
-        <v>76</v>
-      </c>
-      <c r="E140" t="s">
-        <v>14</v>
-      </c>
-      <c r="F140" t="s">
-        <v>89</v>
-      </c>
-      <c r="G140" t="s">
-        <v>65</v>
+      <c r="A140" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A141" t="s">
-        <v>98</v>
-      </c>
-      <c r="B141" t="s">
-        <v>34</v>
+      <c r="A141" t="str">
+        <f>B133</f>
+        <v>inverter production for home storage system</v>
+      </c>
+      <c r="B141" t="str">
+        <f>B134</f>
+        <v>inverter for home storage system</v>
       </c>
       <c r="C141">
-        <v>0.02</v>
-      </c>
-      <c r="D141" t="s">
-        <v>79</v>
-      </c>
-      <c r="E141" t="s">
-        <v>14</v>
+        <v>1</v>
+      </c>
+      <c r="D141" t="str">
+        <f>B137</f>
+        <v>kilogram</v>
+      </c>
+      <c r="E141" t="str">
+        <f>B135</f>
+        <v>RER</v>
       </c>
       <c r="F141" t="s">
-        <v>89</v>
-      </c>
-      <c r="G141" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B142" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C142">
-        <v>0.45</v>
+        <v>0.06</v>
       </c>
       <c r="D142" t="s">
         <v>76</v>
@@ -3413,67 +3538,67 @@
         <v>89</v>
       </c>
       <c r="G142" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="B143" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C143">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="D143" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E143" t="s">
-        <v>116</v>
+        <v>14</v>
       </c>
       <c r="F143" t="s">
         <v>89</v>
       </c>
       <c r="G143" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B144" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C144">
-        <v>1</v>
+        <v>0.03</v>
       </c>
       <c r="D144" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E144" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F144" t="s">
         <v>89</v>
       </c>
       <c r="G144" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B145" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C145">
-        <v>8</v>
+        <v>0.04</v>
       </c>
       <c r="D145" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E145" t="s">
         <v>14</v>
@@ -3482,1107 +3607,1334 @@
         <v>89</v>
       </c>
       <c r="G145" t="s">
-        <v>67</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>94</v>
+      </c>
+      <c r="B146" t="s">
+        <v>30</v>
+      </c>
+      <c r="C146">
+        <v>0.01</v>
+      </c>
+      <c r="D146" t="s">
+        <v>76</v>
+      </c>
+      <c r="E146" t="s">
+        <v>14</v>
+      </c>
+      <c r="F146" t="s">
+        <v>89</v>
+      </c>
+      <c r="G146" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A147" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>112</v>
+      <c r="A147" t="s">
+        <v>103</v>
+      </c>
+      <c r="B147" t="s">
+        <v>104</v>
+      </c>
+      <c r="C147">
+        <v>0.27</v>
+      </c>
+      <c r="D147" t="s">
+        <v>76</v>
+      </c>
+      <c r="E147" t="s">
+        <v>16</v>
+      </c>
+      <c r="F147" t="s">
+        <v>89</v>
+      </c>
+      <c r="G147" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="B148" t="s">
-        <v>113</v>
+        <v>31</v>
+      </c>
+      <c r="C148">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D148" t="s">
+        <v>76</v>
+      </c>
+      <c r="E148" t="s">
+        <v>14</v>
+      </c>
+      <c r="F148" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="B149" t="s">
-        <v>16</v>
+        <v>32</v>
+      </c>
+      <c r="C149">
+        <v>0.05</v>
+      </c>
+      <c r="D149" t="s">
+        <v>76</v>
+      </c>
+      <c r="E149" t="s">
+        <v>14</v>
+      </c>
+      <c r="F149" t="s">
+        <v>89</v>
+      </c>
+      <c r="G149" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>2</v>
-      </c>
-      <c r="B150">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="B150" t="s">
+        <v>33</v>
+      </c>
+      <c r="C150">
+        <v>0.45</v>
+      </c>
+      <c r="D150" t="s">
+        <v>76</v>
+      </c>
+      <c r="E150" t="s">
+        <v>14</v>
+      </c>
+      <c r="F150" t="s">
+        <v>89</v>
+      </c>
+      <c r="G150" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="B151" t="s">
-        <v>76</v>
+        <v>34</v>
+      </c>
+      <c r="C151">
+        <v>0.02</v>
+      </c>
+      <c r="D151" t="s">
+        <v>79</v>
+      </c>
+      <c r="E151" t="s">
+        <v>14</v>
+      </c>
+      <c r="F151" t="s">
+        <v>89</v>
+      </c>
+      <c r="G151" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="B152" t="s">
-        <v>75</v>
+        <v>35</v>
+      </c>
+      <c r="C152">
+        <v>0.45</v>
+      </c>
+      <c r="D152" t="s">
+        <v>76</v>
+      </c>
+      <c r="E152" t="s">
+        <v>14</v>
+      </c>
+      <c r="F152" t="s">
+        <v>89</v>
+      </c>
+      <c r="G152" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>9</v>
+        <v>100</v>
+      </c>
+      <c r="B153" t="s">
+        <v>36</v>
+      </c>
+      <c r="C153">
+        <v>1</v>
+      </c>
+      <c r="D153" t="s">
+        <v>78</v>
+      </c>
+      <c r="E153" t="s">
+        <v>116</v>
+      </c>
+      <c r="F153" t="s">
+        <v>89</v>
+      </c>
+      <c r="G153" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A154" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G154" s="1" t="s">
-        <v>7</v>
+      <c r="A154" t="s">
+        <v>84</v>
+      </c>
+      <c r="B154" t="s">
+        <v>13</v>
+      </c>
+      <c r="C154">
+        <v>1</v>
+      </c>
+      <c r="D154" t="s">
+        <v>78</v>
+      </c>
+      <c r="E154" t="s">
+        <v>16</v>
+      </c>
+      <c r="F154" t="s">
+        <v>89</v>
+      </c>
+      <c r="G154" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A155" t="str">
-        <f>B147</f>
-        <v>cell module production, LFP, for home storage system</v>
-      </c>
-      <c r="B155" t="str">
-        <f>B148</f>
-        <v>cell module, LFP, for home storage system</v>
+      <c r="A155" t="s">
+        <v>101</v>
+      </c>
+      <c r="B155" t="s">
+        <v>37</v>
       </c>
       <c r="C155">
-        <v>1</v>
-      </c>
-      <c r="D155" t="str">
-        <f>B151</f>
-        <v>kilogram</v>
-      </c>
-      <c r="E155" t="str">
-        <f>B149</f>
-        <v>RER</v>
+        <v>8</v>
+      </c>
+      <c r="D155" t="s">
+        <v>78</v>
+      </c>
+      <c r="E155" t="s">
+        <v>14</v>
       </c>
       <c r="F155" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A156" t="s">
-        <v>114</v>
-      </c>
-      <c r="B156" t="s">
-        <v>115</v>
-      </c>
-      <c r="C156">
-        <v>0.03</v>
-      </c>
-      <c r="D156" t="s">
-        <v>76</v>
-      </c>
-      <c r="E156" t="s">
-        <v>16</v>
-      </c>
-      <c r="F156" t="s">
-        <v>89</v>
-      </c>
-      <c r="G156" t="s">
-        <v>68</v>
+        <v>89</v>
+      </c>
+      <c r="G155" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A157" t="s">
-        <v>118</v>
-      </c>
-      <c r="B157" t="s">
-        <v>117</v>
-      </c>
-      <c r="C157">
-        <v>0.63</v>
-      </c>
-      <c r="D157" t="s">
-        <v>76</v>
-      </c>
-      <c r="E157" t="s">
-        <v>14</v>
-      </c>
-      <c r="F157" t="s">
-        <v>89</v>
-      </c>
-      <c r="G157" t="s">
-        <v>69</v>
+      <c r="A157" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="B158" t="s">
-        <v>33</v>
-      </c>
-      <c r="C158">
-        <v>0.34</v>
-      </c>
-      <c r="D158" t="s">
-        <v>76</v>
-      </c>
-      <c r="E158" t="s">
-        <v>14</v>
-      </c>
-      <c r="F158" t="s">
-        <v>89</v>
-      </c>
-      <c r="G158" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="B159" t="s">
-        <v>35</v>
-      </c>
-      <c r="C159">
-        <v>0.34</v>
-      </c>
-      <c r="D159" t="s">
-        <v>76</v>
-      </c>
-      <c r="E159" t="s">
-        <v>14</v>
-      </c>
-      <c r="F159" t="s">
-        <v>89</v>
-      </c>
-      <c r="G159" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>100</v>
-      </c>
-      <c r="B160" t="s">
-        <v>36</v>
-      </c>
-      <c r="C160">
-        <v>1</v>
-      </c>
-      <c r="D160" t="s">
-        <v>78</v>
-      </c>
-      <c r="E160" t="s">
-        <v>116</v>
-      </c>
-      <c r="F160" t="s">
-        <v>89</v>
-      </c>
-      <c r="G160" t="s">
-        <v>49</v>
+        <v>2</v>
+      </c>
+      <c r="B160">
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="B161" t="s">
-        <v>13</v>
-      </c>
-      <c r="C161">
-        <v>1</v>
-      </c>
-      <c r="D161" t="s">
-        <v>78</v>
-      </c>
-      <c r="E161" t="s">
-        <v>16</v>
-      </c>
-      <c r="F161" t="s">
-        <v>89</v>
-      </c>
-      <c r="G161" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="B162" t="s">
-        <v>37</v>
-      </c>
-      <c r="C162">
-        <v>8</v>
-      </c>
-      <c r="D162" t="s">
-        <v>78</v>
-      </c>
-      <c r="E162" t="s">
-        <v>14</v>
-      </c>
-      <c r="F162" t="s">
-        <v>89</v>
-      </c>
-      <c r="G162" t="s">
-        <v>67</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>128</v>
+        <v>1</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A165" t="s">
-        <v>1</v>
-      </c>
-      <c r="B165" t="s">
-        <v>129</v>
+      <c r="A165" t="str">
+        <f>B157</f>
+        <v>cell module production, LFP, for home storage system</v>
+      </c>
+      <c r="B165" t="str">
+        <f>B158</f>
+        <v>cell module, LFP, for home storage system</v>
+      </c>
+      <c r="C165">
+        <v>1</v>
+      </c>
+      <c r="D165" t="str">
+        <f>B161</f>
+        <v>kilogram</v>
+      </c>
+      <c r="E165" t="str">
+        <f>B159</f>
+        <v>RER</v>
+      </c>
+      <c r="F165" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="B166" t="s">
+        <v>115</v>
+      </c>
+      <c r="C166">
+        <v>0.03</v>
+      </c>
+      <c r="D166" t="s">
+        <v>76</v>
+      </c>
+      <c r="E166" t="s">
         <v>16</v>
+      </c>
+      <c r="F166" t="s">
+        <v>89</v>
+      </c>
+      <c r="G166" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>2</v>
-      </c>
-      <c r="B167">
-        <v>1</v>
+        <v>118</v>
+      </c>
+      <c r="B167" t="s">
+        <v>117</v>
+      </c>
+      <c r="C167">
+        <v>0.63</v>
+      </c>
+      <c r="D167" t="s">
+        <v>76</v>
+      </c>
+      <c r="E167" t="s">
+        <v>14</v>
+      </c>
+      <c r="F167" t="s">
+        <v>89</v>
+      </c>
+      <c r="G167" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="B168" t="s">
-        <v>76</v>
+        <v>33</v>
+      </c>
+      <c r="C168">
+        <v>0.34</v>
+      </c>
+      <c r="D168" t="s">
+        <v>76</v>
+      </c>
+      <c r="E168" t="s">
+        <v>14</v>
+      </c>
+      <c r="F168" t="s">
+        <v>89</v>
+      </c>
+      <c r="G168" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="B169" t="s">
-        <v>75</v>
+        <v>35</v>
+      </c>
+      <c r="C169">
+        <v>0.34</v>
+      </c>
+      <c r="D169" t="s">
+        <v>76</v>
+      </c>
+      <c r="E169" t="s">
+        <v>14</v>
+      </c>
+      <c r="F169" t="s">
+        <v>89</v>
+      </c>
+      <c r="G169" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>9</v>
+        <v>100</v>
+      </c>
+      <c r="B170" t="s">
+        <v>36</v>
+      </c>
+      <c r="C170">
+        <v>1</v>
+      </c>
+      <c r="D170" t="s">
+        <v>78</v>
+      </c>
+      <c r="E170" t="s">
+        <v>116</v>
+      </c>
+      <c r="F170" t="s">
+        <v>89</v>
+      </c>
+      <c r="G170" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A171" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G171" s="1" t="s">
-        <v>7</v>
+      <c r="A171" t="s">
+        <v>84</v>
+      </c>
+      <c r="B171" t="s">
+        <v>13</v>
+      </c>
+      <c r="C171">
+        <v>1</v>
+      </c>
+      <c r="D171" t="s">
+        <v>78</v>
+      </c>
+      <c r="E171" t="s">
+        <v>16</v>
+      </c>
+      <c r="F171" t="s">
+        <v>89</v>
+      </c>
+      <c r="G171" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A172" t="str">
-        <f>B164</f>
-        <v>cell module production, NMC811, for home storage system</v>
-      </c>
-      <c r="B172" t="str">
-        <f>B165</f>
-        <v>cell module, NMC811, for home storage system</v>
+      <c r="A172" t="s">
+        <v>101</v>
+      </c>
+      <c r="B172" t="s">
+        <v>37</v>
       </c>
       <c r="C172">
-        <v>1</v>
-      </c>
-      <c r="D172" t="str">
-        <f>B168</f>
-        <v>kilogram</v>
-      </c>
-      <c r="E172" t="str">
-        <f>B166</f>
-        <v>RER</v>
+        <v>8</v>
+      </c>
+      <c r="D172" t="s">
+        <v>78</v>
+      </c>
+      <c r="E172" t="s">
+        <v>14</v>
       </c>
       <c r="F172" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A173" t="s">
-        <v>114</v>
-      </c>
-      <c r="B173" t="s">
-        <v>115</v>
-      </c>
-      <c r="C173">
-        <v>0.03</v>
-      </c>
-      <c r="D173" t="s">
-        <v>76</v>
-      </c>
-      <c r="E173" t="s">
-        <v>16</v>
-      </c>
-      <c r="F173" t="s">
-        <v>89</v>
-      </c>
-      <c r="G173" t="s">
-        <v>68</v>
+        <v>89</v>
+      </c>
+      <c r="G172" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A174" t="s">
-        <v>125</v>
-      </c>
-      <c r="B174" t="s">
-        <v>126</v>
-      </c>
-      <c r="C174">
-        <v>0.63</v>
-      </c>
-      <c r="D174" t="s">
-        <v>76</v>
-      </c>
-      <c r="E174" t="s">
-        <v>14</v>
-      </c>
-      <c r="F174" t="s">
-        <v>89</v>
-      </c>
-      <c r="G174" t="s">
-        <v>69</v>
+      <c r="A174" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="B175" t="s">
-        <v>33</v>
-      </c>
-      <c r="C175">
-        <v>0.34</v>
-      </c>
-      <c r="D175" t="s">
-        <v>76</v>
-      </c>
-      <c r="E175" t="s">
-        <v>14</v>
-      </c>
-      <c r="F175" t="s">
-        <v>89</v>
-      </c>
-      <c r="G175" t="s">
-        <v>65</v>
+        <v>129</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="B176" t="s">
-        <v>35</v>
-      </c>
-      <c r="C176">
-        <v>0.34</v>
-      </c>
-      <c r="D176" t="s">
-        <v>76</v>
-      </c>
-      <c r="E176" t="s">
-        <v>14</v>
-      </c>
-      <c r="F176" t="s">
-        <v>89</v>
-      </c>
-      <c r="G176" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>100</v>
-      </c>
-      <c r="B177" t="s">
-        <v>36</v>
-      </c>
-      <c r="C177">
-        <v>1</v>
-      </c>
-      <c r="D177" t="s">
-        <v>78</v>
-      </c>
-      <c r="E177" t="s">
-        <v>116</v>
-      </c>
-      <c r="F177" t="s">
-        <v>89</v>
-      </c>
-      <c r="G177" t="s">
-        <v>49</v>
+        <v>2</v>
+      </c>
+      <c r="B177">
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="B178" t="s">
-        <v>13</v>
-      </c>
-      <c r="C178">
-        <v>1</v>
-      </c>
-      <c r="D178" t="s">
-        <v>78</v>
-      </c>
-      <c r="E178" t="s">
-        <v>16</v>
-      </c>
-      <c r="F178" t="s">
-        <v>89</v>
-      </c>
-      <c r="G178" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="B179" t="s">
-        <v>37</v>
-      </c>
-      <c r="C179">
-        <v>8</v>
-      </c>
-      <c r="D179" t="s">
-        <v>78</v>
-      </c>
-      <c r="E179" t="s">
-        <v>14</v>
-      </c>
-      <c r="F179" t="s">
-        <v>89</v>
-      </c>
-      <c r="G179" t="s">
-        <v>67</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>114</v>
+        <v>1</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A182" t="s">
-        <v>1</v>
-      </c>
-      <c r="B182" t="s">
-        <v>115</v>
+      <c r="A182" t="str">
+        <f>B174</f>
+        <v>cell module production, NMC811, for home storage system</v>
+      </c>
+      <c r="B182" t="str">
+        <f>B175</f>
+        <v>cell module, NMC811, for home storage system</v>
+      </c>
+      <c r="C182">
+        <v>1</v>
+      </c>
+      <c r="D182" t="str">
+        <f>B178</f>
+        <v>kilogram</v>
+      </c>
+      <c r="E182" t="str">
+        <f>B176</f>
+        <v>RER</v>
+      </c>
+      <c r="F182" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="B183" t="s">
+        <v>115</v>
+      </c>
+      <c r="C183">
+        <v>0.03</v>
+      </c>
+      <c r="D183" t="s">
+        <v>76</v>
+      </c>
+      <c r="E183" t="s">
         <v>16</v>
+      </c>
+      <c r="F183" t="s">
+        <v>89</v>
+      </c>
+      <c r="G183" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>2</v>
-      </c>
-      <c r="B184">
-        <v>1</v>
+        <v>125</v>
+      </c>
+      <c r="B184" t="s">
+        <v>126</v>
+      </c>
+      <c r="C184">
+        <v>0.63</v>
+      </c>
+      <c r="D184" t="s">
+        <v>76</v>
+      </c>
+      <c r="E184" t="s">
+        <v>14</v>
+      </c>
+      <c r="F184" t="s">
+        <v>89</v>
+      </c>
+      <c r="G184" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="B185" t="s">
-        <v>76</v>
+        <v>33</v>
+      </c>
+      <c r="C185">
+        <v>0.34</v>
+      </c>
+      <c r="D185" t="s">
+        <v>76</v>
+      </c>
+      <c r="E185" t="s">
+        <v>14</v>
+      </c>
+      <c r="F185" t="s">
+        <v>89</v>
+      </c>
+      <c r="G185" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="B186" t="s">
-        <v>75</v>
+        <v>35</v>
+      </c>
+      <c r="C186">
+        <v>0.34</v>
+      </c>
+      <c r="D186" t="s">
+        <v>76</v>
+      </c>
+      <c r="E186" t="s">
+        <v>14</v>
+      </c>
+      <c r="F186" t="s">
+        <v>89</v>
+      </c>
+      <c r="G186" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>9</v>
+        <v>100</v>
+      </c>
+      <c r="B187" t="s">
+        <v>36</v>
+      </c>
+      <c r="C187">
+        <v>1</v>
+      </c>
+      <c r="D187" t="s">
+        <v>78</v>
+      </c>
+      <c r="E187" t="s">
+        <v>116</v>
+      </c>
+      <c r="F187" t="s">
+        <v>89</v>
+      </c>
+      <c r="G187" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A188" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F188" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G188" s="1" t="s">
-        <v>7</v>
+      <c r="A188" t="s">
+        <v>84</v>
+      </c>
+      <c r="B188" t="s">
+        <v>13</v>
+      </c>
+      <c r="C188">
+        <v>1</v>
+      </c>
+      <c r="D188" t="s">
+        <v>78</v>
+      </c>
+      <c r="E188" t="s">
+        <v>16</v>
+      </c>
+      <c r="F188" t="s">
+        <v>89</v>
+      </c>
+      <c r="G188" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A189" t="str">
-        <f>B181</f>
-        <v>battery module system production</v>
-      </c>
-      <c r="B189" t="str">
-        <f>B182</f>
-        <v>battery module system for home storage system module</v>
+      <c r="A189" t="s">
+        <v>101</v>
+      </c>
+      <c r="B189" t="s">
+        <v>37</v>
       </c>
       <c r="C189">
-        <v>1</v>
-      </c>
-      <c r="D189" t="str">
-        <f>B185</f>
-        <v>kilogram</v>
-      </c>
-      <c r="E189" t="str">
-        <f>B183</f>
-        <v>RER</v>
+        <v>8</v>
+      </c>
+      <c r="D189" t="s">
+        <v>78</v>
+      </c>
+      <c r="E189" t="s">
+        <v>14</v>
       </c>
       <c r="F189" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A190" t="s">
-        <v>90</v>
-      </c>
-      <c r="B190" t="s">
-        <v>26</v>
-      </c>
-      <c r="C190">
-        <v>0.64</v>
-      </c>
-      <c r="D190" t="s">
-        <v>76</v>
-      </c>
-      <c r="E190" t="s">
-        <v>14</v>
-      </c>
-      <c r="F190" t="s">
-        <v>89</v>
-      </c>
-      <c r="G190" t="s">
-        <v>38</v>
+        <v>89</v>
+      </c>
+      <c r="G189" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A191" t="s">
-        <v>81</v>
-      </c>
-      <c r="B191" t="s">
-        <v>10</v>
-      </c>
-      <c r="C191">
-        <v>0.03</v>
-      </c>
-      <c r="D191" t="s">
-        <v>76</v>
-      </c>
-      <c r="E191" t="s">
-        <v>14</v>
-      </c>
-      <c r="F191" t="s">
-        <v>89</v>
-      </c>
-      <c r="G191" t="s">
-        <v>18</v>
+      <c r="A191" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="B192" t="s">
-        <v>27</v>
-      </c>
-      <c r="C192">
-        <v>0.03</v>
-      </c>
-      <c r="D192" t="s">
-        <v>76</v>
-      </c>
-      <c r="E192" t="s">
-        <v>14</v>
-      </c>
-      <c r="F192" t="s">
-        <v>89</v>
-      </c>
-      <c r="G192" t="s">
-        <v>39</v>
+        <v>115</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="B193" t="s">
-        <v>32</v>
-      </c>
-      <c r="C193">
-        <v>0.64</v>
-      </c>
-      <c r="D193" t="s">
-        <v>76</v>
-      </c>
-      <c r="E193" t="s">
-        <v>14</v>
-      </c>
-      <c r="F193" t="s">
-        <v>89</v>
-      </c>
-      <c r="G193" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>98</v>
-      </c>
-      <c r="B194" t="s">
-        <v>34</v>
-      </c>
-      <c r="C194">
-        <v>0.09</v>
-      </c>
-      <c r="D194" t="s">
-        <v>79</v>
-      </c>
-      <c r="E194" t="s">
-        <v>14</v>
-      </c>
-      <c r="F194" t="s">
-        <v>89</v>
-      </c>
-      <c r="G194" t="s">
-        <v>66</v>
+        <v>2</v>
+      </c>
+      <c r="B194">
+        <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="B195" t="s">
-        <v>36</v>
-      </c>
-      <c r="C195">
-        <v>0.2</v>
-      </c>
-      <c r="D195" t="s">
-        <v>78</v>
-      </c>
-      <c r="E195" t="s">
-        <v>116</v>
-      </c>
-      <c r="F195" t="s">
-        <v>89</v>
-      </c>
-      <c r="G195" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="B196" t="s">
-        <v>13</v>
-      </c>
-      <c r="C196">
-        <v>0.1</v>
-      </c>
-      <c r="D196" t="s">
-        <v>78</v>
-      </c>
-      <c r="E196" t="s">
-        <v>16</v>
-      </c>
-      <c r="F196" t="s">
-        <v>89</v>
-      </c>
-      <c r="G196" t="s">
-        <v>25</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>119</v>
+        <v>1</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A199" t="s">
-        <v>1</v>
-      </c>
-      <c r="B199" t="s">
-        <v>120</v>
+      <c r="A199" t="str">
+        <f>B191</f>
+        <v>battery module system production</v>
+      </c>
+      <c r="B199" t="str">
+        <f>B192</f>
+        <v>battery module system for home storage system module</v>
+      </c>
+      <c r="C199">
+        <v>1</v>
+      </c>
+      <c r="D199" t="str">
+        <f>B195</f>
+        <v>kilogram</v>
+      </c>
+      <c r="E199" t="str">
+        <f>B193</f>
+        <v>RER</v>
+      </c>
+      <c r="F199" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="B200" t="s">
-        <v>16</v>
+        <v>26</v>
+      </c>
+      <c r="C200">
+        <v>0.64</v>
+      </c>
+      <c r="D200" t="s">
+        <v>76</v>
+      </c>
+      <c r="E200" t="s">
+        <v>14</v>
+      </c>
+      <c r="F200" t="s">
+        <v>89</v>
+      </c>
+      <c r="G200" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>2</v>
-      </c>
-      <c r="B201">
-        <v>1</v>
+        <v>81</v>
+      </c>
+      <c r="B201" t="s">
+        <v>10</v>
+      </c>
+      <c r="C201">
+        <v>0.03</v>
+      </c>
+      <c r="D201" t="s">
+        <v>76</v>
+      </c>
+      <c r="E201" t="s">
+        <v>14</v>
+      </c>
+      <c r="F201" t="s">
+        <v>89</v>
+      </c>
+      <c r="G201" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
       <c r="B202" t="s">
-        <v>76</v>
+        <v>27</v>
+      </c>
+      <c r="C202">
+        <v>0.03</v>
+      </c>
+      <c r="D202" t="s">
+        <v>76</v>
+      </c>
+      <c r="E202" t="s">
+        <v>14</v>
+      </c>
+      <c r="F202" t="s">
+        <v>89</v>
+      </c>
+      <c r="G202" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>7</v>
+        <v>96</v>
       </c>
       <c r="B203" t="s">
-        <v>75</v>
+        <v>32</v>
+      </c>
+      <c r="C203">
+        <v>0.64</v>
+      </c>
+      <c r="D203" t="s">
+        <v>76</v>
+      </c>
+      <c r="E203" t="s">
+        <v>14</v>
+      </c>
+      <c r="F203" t="s">
+        <v>89</v>
+      </c>
+      <c r="G203" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>9</v>
+        <v>98</v>
+      </c>
+      <c r="B204" t="s">
+        <v>34</v>
+      </c>
+      <c r="C204">
+        <v>0.09</v>
+      </c>
+      <c r="D204" t="s">
+        <v>79</v>
+      </c>
+      <c r="E204" t="s">
+        <v>14</v>
+      </c>
+      <c r="F204" t="s">
+        <v>89</v>
+      </c>
+      <c r="G204" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A205" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C205" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F205" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G205" s="1" t="s">
-        <v>7</v>
+      <c r="A205" t="s">
+        <v>100</v>
+      </c>
+      <c r="B205" t="s">
+        <v>36</v>
+      </c>
+      <c r="C205">
+        <v>0.2</v>
+      </c>
+      <c r="D205" t="s">
+        <v>78</v>
+      </c>
+      <c r="E205" t="s">
+        <v>116</v>
+      </c>
+      <c r="F205" t="s">
+        <v>89</v>
+      </c>
+      <c r="G205" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A206" t="str">
-        <f>B198</f>
-        <v>system controller production, for home storage system</v>
-      </c>
-      <c r="B206" t="str">
-        <f>B199</f>
-        <v>system controller, for home storage system</v>
+      <c r="A206" t="s">
+        <v>84</v>
+      </c>
+      <c r="B206" t="s">
+        <v>13</v>
       </c>
       <c r="C206">
-        <v>1</v>
-      </c>
-      <c r="D206" t="str">
-        <f>B202</f>
-        <v>kilogram</v>
-      </c>
-      <c r="E206" t="str">
-        <f>B200</f>
-        <v>RER</v>
+        <v>0.1</v>
+      </c>
+      <c r="D206" t="s">
+        <v>78</v>
+      </c>
+      <c r="E206" t="s">
+        <v>16</v>
       </c>
       <c r="F206" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A207" t="s">
-        <v>114</v>
-      </c>
-      <c r="B207" t="s">
-        <v>115</v>
-      </c>
-      <c r="C207">
-        <v>0.17</v>
-      </c>
-      <c r="D207" t="s">
-        <v>76</v>
-      </c>
-      <c r="E207" t="s">
-        <v>16</v>
-      </c>
-      <c r="F207" t="s">
-        <v>89</v>
-      </c>
-      <c r="G207" t="s">
-        <v>72</v>
+        <v>89</v>
+      </c>
+      <c r="G206" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A208" t="s">
-        <v>83</v>
-      </c>
-      <c r="B208" t="s">
-        <v>12</v>
-      </c>
-      <c r="C208">
-        <v>0.32</v>
-      </c>
-      <c r="D208" t="s">
-        <v>76</v>
-      </c>
-      <c r="E208" t="s">
-        <v>14</v>
-      </c>
-      <c r="F208" t="s">
-        <v>89</v>
-      </c>
-      <c r="G208" t="s">
-        <v>20</v>
+      <c r="A208" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="B209" t="s">
-        <v>33</v>
-      </c>
-      <c r="C209">
-        <v>0.44</v>
-      </c>
-      <c r="D209" t="s">
-        <v>76</v>
-      </c>
-      <c r="E209" t="s">
-        <v>14</v>
-      </c>
-      <c r="F209" t="s">
-        <v>89</v>
-      </c>
-      <c r="G209" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>121</v>
+        <v>4</v>
       </c>
       <c r="B210" t="s">
-        <v>70</v>
-      </c>
-      <c r="C210">
-        <v>0.03</v>
-      </c>
-      <c r="D210" t="s">
-        <v>3</v>
-      </c>
-      <c r="E210" t="s">
-        <v>14</v>
-      </c>
-      <c r="F210" t="s">
-        <v>89</v>
-      </c>
-      <c r="G210" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>99</v>
-      </c>
-      <c r="B211" t="s">
-        <v>35</v>
-      </c>
-      <c r="C211">
-        <v>0.44</v>
-      </c>
-      <c r="D211" t="s">
-        <v>76</v>
-      </c>
-      <c r="E211" t="s">
-        <v>14</v>
-      </c>
-      <c r="F211" t="s">
-        <v>89</v>
-      </c>
-      <c r="G211" t="s">
-        <v>48</v>
+        <v>2</v>
+      </c>
+      <c r="B211">
+        <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
+        <v>3</v>
+      </c>
+      <c r="B212" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A213" t="s">
+        <v>7</v>
+      </c>
+      <c r="B213" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A214" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A215" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G215" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A216" t="str">
+        <f>B208</f>
+        <v>system controller production, for home storage system</v>
+      </c>
+      <c r="B216" t="str">
+        <f>B209</f>
+        <v>system controller, for home storage system</v>
+      </c>
+      <c r="C216">
+        <v>1</v>
+      </c>
+      <c r="D216" t="str">
+        <f>B212</f>
+        <v>kilogram</v>
+      </c>
+      <c r="E216" t="str">
+        <f>B210</f>
+        <v>RER</v>
+      </c>
+      <c r="F216" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A217" t="s">
+        <v>114</v>
+      </c>
+      <c r="B217" t="s">
+        <v>115</v>
+      </c>
+      <c r="C217">
+        <v>0.17</v>
+      </c>
+      <c r="D217" t="s">
+        <v>76</v>
+      </c>
+      <c r="E217" t="s">
+        <v>16</v>
+      </c>
+      <c r="F217" t="s">
+        <v>89</v>
+      </c>
+      <c r="G217" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A218" t="s">
+        <v>83</v>
+      </c>
+      <c r="B218" t="s">
+        <v>12</v>
+      </c>
+      <c r="C218">
+        <v>0.32</v>
+      </c>
+      <c r="D218" t="s">
+        <v>76</v>
+      </c>
+      <c r="E218" t="s">
+        <v>14</v>
+      </c>
+      <c r="F218" t="s">
+        <v>89</v>
+      </c>
+      <c r="G218" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A219" t="s">
+        <v>97</v>
+      </c>
+      <c r="B219" t="s">
+        <v>33</v>
+      </c>
+      <c r="C219">
+        <v>0.44</v>
+      </c>
+      <c r="D219" t="s">
+        <v>76</v>
+      </c>
+      <c r="E219" t="s">
+        <v>14</v>
+      </c>
+      <c r="F219" t="s">
+        <v>89</v>
+      </c>
+      <c r="G219" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A220" t="s">
+        <v>121</v>
+      </c>
+      <c r="B220" t="s">
+        <v>70</v>
+      </c>
+      <c r="C220">
+        <v>0.03</v>
+      </c>
+      <c r="D220" t="s">
+        <v>3</v>
+      </c>
+      <c r="E220" t="s">
+        <v>14</v>
+      </c>
+      <c r="F220" t="s">
+        <v>89</v>
+      </c>
+      <c r="G220" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>99</v>
+      </c>
+      <c r="B221" t="s">
+        <v>35</v>
+      </c>
+      <c r="C221">
+        <v>0.44</v>
+      </c>
+      <c r="D221" t="s">
+        <v>76</v>
+      </c>
+      <c r="E221" t="s">
+        <v>14</v>
+      </c>
+      <c r="F221" t="s">
+        <v>89</v>
+      </c>
+      <c r="G221" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A222" t="s">
         <v>122</v>
       </c>
-      <c r="B212" t="s">
+      <c r="B222" t="s">
         <v>71</v>
       </c>
-      <c r="C212">
+      <c r="C222">
         <v>0.02</v>
       </c>
-      <c r="D212" t="s">
-        <v>76</v>
-      </c>
-      <c r="E212" t="s">
+      <c r="D222" t="s">
+        <v>76</v>
+      </c>
+      <c r="E222" t="s">
         <v>14</v>
       </c>
-      <c r="F212" t="s">
-        <v>89</v>
-      </c>
-      <c r="G212" t="s">
+      <c r="F222" t="s">
+        <v>89</v>
+      </c>
+      <c r="G222" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
+    <row r="225">
+      <c r="A225" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="B225" t="inlineStr">
         <is>
           <t xml:space="preserve">battery module production, home storage, Li-ion, LFP, 14.4 kWh</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
+    <row r="226">
+      <c r="A226" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>RER</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
+    <row r="227">
+      <c r="A227" t="inlineStr">
         <is>
           <t>production amount</t>
         </is>
       </c>
-      <c r="B217">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
+      <c r="B227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
         <is>
           <t>reference product</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B228" t="inlineStr">
         <is>
           <t xml:space="preserve">battery module, home storage, Li-ion, LFP, 14.4 kWh</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
+    <row r="229">
+      <c r="A229" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B229" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
+    <row r="230">
+      <c r="A230" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B230" t="inlineStr">
         <is>
           <t>Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells.</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
+    <row r="231">
+      <c r="A231" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B231" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: cell modules, home 14.4kWh LFP, capacity-consistent reference. Former reference product: cell modules, home 14.4kWh LFP, capacity-consistent reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED HOME-STORAGE COMPONENT LIFE BUDGETS, issue67,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899 Table3,minimum/maximum calendar and cyclelife. Recompute for retained13years/2500cycles,NOT copy published20year/7300cycle factors. For eachcomponent selecthigh/lowmanufacturedsets=max(1,systemyears/componentyears,systemcycles/componentcycles),usingpairedlow/highlife endpoints,then midpointsets as engineeringexpectedlifetimeattribution. Clampatonebecauseanewcompleteinstalledsetisrequired; no assumedreusecredit for residualcomponentlife. This is not a probabilisticfailure distribution or literal fractionalinstallation. ReferenceLFPcellsets1,NMC811cellsets1.125;charger/inverter/controls/moduleBMSsets1.3125;cables1.15;housing/module steel1.0. Sourcepublished1.96/2.43cell and1.92electronics factors refer20years/7300cycles andmustnot be blindly transferred. Each home system activity now means an installeddesignplusits13yearmanufacturingreplacementbudget; labelsnominalkWhstayinstalledcapacity,not manufacturedcapacitysum. Multiplycellmanufactureonly bycellfactor within newunitmodule; moduleBMS follows electronicsfactor,modulesteel/rolling remainoneinstalledset. Externalsteelhousingremainsone,externalcontroller/electronics,charger,inverter andcablesfollowtheir own factors. Do not multiplythewholemodule anditscellsagain or buyanotherfullhome systemfor inverterfailure. Increasecomponentfreight withactualmanufacturedcomponentmass; retaininitialassemblyelectricityonce because source replacementassemblyenergy is unspecified,which remains a coveragegap. Existing servicewrapperstays1/consumerlifetimekWh fromissue66; operatingelectricity,DoD,nominalinstalledcapacity andcalendarhorizonunchanged. Transportation is at original routeintensities; packaging/maintenance labour and returntransport are gaps. Device-specific treatment/recycling is not invented; no recoverycredits orprimarysecondaryshares added. Future electronicsdurability is a sourceassumption,not verifiedmodernfleetlife. Sensitivityuseslistedmin/maxsets andsourcecalendar/cyclelimits. Numericreference:{"LFP":{"min_sets":1,"max_sets":1,"reference_sets":1.0},"NMC811":{"min_sets":1,"max_sets":1.25,"reference_sets":1.125},"electronics":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"inverter":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"charger":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"cable":{"min_sets":1,"max_sets":1.3,"reference_sets":1.15},"housing":{"min_sets":1,"max_sets":1,"reference_sets":1.0}}
@@ -4591,417 +4943,417 @@
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
+    <row r="232">
+      <c r="A232" t="inlineStr">
         <is>
           <t>Exchanges</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
+    <row r="233">
+      <c r="A233" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B233" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
+      <c r="C233" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D233" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="E233" t="inlineStr">
         <is>
           <t>categories</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
+      <c r="F233" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
+      <c r="G233" t="inlineStr">
         <is>
           <t>reference product</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
+      <c r="H233" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr">
+      <c r="I233" t="inlineStr">
         <is>
           <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery module production, home storage, Li-ion, LFP, 14.4 kWh</t>
-        </is>
-      </c>
-      <c r="B224">
-        <v>1</v>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery module, home storage, Li-ion, LFP, 14.4 kWh</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery module, home storage, Li-ion, LFP, 14.4 kWh</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>battery module system production</t>
-        </is>
-      </c>
-      <c r="B225">
-        <v>6.3504000000000005</v>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>battery module system for home storage system module</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>battery module system for home storage system module</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>market for battery cell, Li-ion, LFP</t>
-        </is>
-      </c>
-      <c r="B226">
-        <v>90.0</v>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>battery cell, Li-ion, LFP</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>battery cell, Li-ion, LFP</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>market for metal working, average for steel product manufacturing</t>
-        </is>
-      </c>
-      <c r="B227">
-        <v>54.83520000000001</v>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>metal working, average for steel product manufacturing</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>metal working, average for steel product manufacturing</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>market for steel, low-alloyed</t>
-        </is>
-      </c>
-      <c r="B228">
-        <v>54.83520000000001</v>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>steel, low-alloyed</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>steel, low-alloyed</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>market for transport, freight train</t>
-        </is>
-      </c>
-      <c r="B229">
-        <v>151.1856</v>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Europe without Switzerland</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>ton kilometer</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>transport, freight train</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>transport, freight train</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>market for transport, freight, lorry 16-32 metric ton, EURO5</t>
-        </is>
-      </c>
-      <c r="B230">
-        <v>151.1856</v>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>ton kilometer</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>market for transport, freight, sea, container ship</t>
-        </is>
-      </c>
-      <c r="B231">
-        <v>1209.4848</v>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>ton kilometer</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>transport, freight, sea, container ship</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>transport, freight, sea, container ship</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery module production, home storage, Li-ion, NMC811, 19.5 kWh</t>
+          <t xml:space="preserve">battery module production, home storage, Li-ion, LFP, 14.4 kWh</t>
+        </is>
+      </c>
+      <c r="B234">
+        <v>1</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">battery module, home storage, Li-ion, LFP, 14.4 kWh</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">battery module, home storage, Li-ion, LFP, 14.4 kWh</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
+          <t>battery module system production</t>
+        </is>
+      </c>
+      <c r="B235">
+        <v>6.3504000000000005</v>
+      </c>
+      <c r="C235" t="inlineStr">
         <is>
           <t>RER</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>battery module system for home storage system module</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>battery module system for home storage system module</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>production amount</t>
+          <t>market for battery cell, Li-ion, LFP</t>
         </is>
       </c>
       <c r="B236">
-        <v>1</v>
+        <v>90.0</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, LFP</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, LFP</t>
+        </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery module, home storage, Li-ion, NMC811, 19.5 kWh</t>
+          <t>market for metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B237">
+        <v>54.83520000000001</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>unit</t>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B238">
+        <v>54.83520000000001</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells.</t>
+          <t>market for transport, freight train</t>
+        </is>
+      </c>
+      <c r="B239">
+        <v>151.1856</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
+          <t>market for transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+      <c r="B240">
+        <v>151.1856</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>market for transport, freight, sea, container ship</t>
+        </is>
+      </c>
+      <c r="B241">
+        <v>1209.4848</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>transport, freight, sea, container ship</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>transport, freight, sea, container ship</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">battery module production, home storage, Li-ion, NMC811, 19.5 kWh</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">battery module, home storage, Li-ion, NMC811, 19.5 kWh</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
+      <c r="B250" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: cell modules, home 19.5kWh NMC811, capacity-consistent reference. Former reference product: cell modules, home 19.5kWh NMC811, capacity-consistent reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED HOME-STORAGE COMPONENT LIFE BUDGETS, issue67,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899 Table3,minimum/maximum calendar and cyclelife. Recompute for retained13years/2500cycles,NOT copy published20year/7300cycle factors. For eachcomponent selecthigh/lowmanufacturedsets=max(1,systemyears/componentyears,systemcycles/componentcycles),usingpairedlow/highlife endpoints,then midpointsets as engineeringexpectedlifetimeattribution. Clampatonebecauseanewcompleteinstalledsetisrequired; no assumedreusecredit for residualcomponentlife. This is not a probabilisticfailure distribution or literal fractionalinstallation. ReferenceLFPcellsets1,NMC811cellsets1.125;charger/inverter/controls/moduleBMSsets1.3125;cables1.15;housing/module steel1.0. Sourcepublished1.96/2.43cell and1.92electronics factors refer20years/7300cycles andmustnot be blindly transferred. Each home system activity now means an installeddesignplusits13yearmanufacturingreplacementbudget; labelsnominalkWhstayinstalledcapacity,not manufacturedcapacitysum. Multiplycellmanufactureonly bycellfactor within newunitmodule; moduleBMS follows electronicsfactor,modulesteel/rolling remainoneinstalledset. Externalsteelhousingremainsone,externalcontroller/electronics,charger,inverter andcablesfollowtheir own factors. Do not multiplythewholemodule anditscellsagain or buyanotherfullhome systemfor inverterfailure. Increasecomponentfreight withactualmanufacturedcomponentmass; retaininitialassemblyelectricityonce because source replacementassemblyenergy is unspecified,which remains a coveragegap. Existing servicewrapperstays1/consumerlifetimekWh fromissue66; operatingelectricity,DoD,nominalinstalledcapacity andcalendarhorizonunchanged. Transportation is at original routeintensities; packaging/maintenance labour and returntransport are gaps. Device-specific treatment/recycling is not invented; no recoverycredits orprimarysecondaryshares added. Future electronicsdurability is a sourceassumption,not verifiedmodernfleetlife. Sensitivityuseslistedmin/maxsets andsourcecalendar/cyclelimits. Numericreference:{"LFP":{"min_sets":1,"max_sets":1,"reference_sets":1.0},"NMC811":{"min_sets":1,"max_sets":1.25,"reference_sets":1.125},"electronics":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"inverter":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"charger":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"cable":{"min_sets":1,"max_sets":1.3,"reference_sets":1.15},"housing":{"min_sets":1,"max_sets":1,"reference_sets":1.0}}
@@ -5010,335 +5362,335 @@
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
+    <row r="251">
+      <c r="A251" t="inlineStr">
         <is>
           <t>Exchanges</t>
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
+    <row r="252">
+      <c r="A252" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
+      <c r="B252" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
+      <c r="C252" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
+      <c r="D252" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
+      <c r="E252" t="inlineStr">
         <is>
           <t>categories</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr">
+      <c r="F252" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr">
+      <c r="G252" t="inlineStr">
         <is>
           <t>reference product</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
+      <c r="H252" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr">
+      <c r="I252" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
+    <row r="253">
+      <c r="A253" t="inlineStr">
         <is>
           <t xml:space="preserve">battery module production, home storage, Li-ion, NMC811, 19.5 kWh</t>
         </is>
       </c>
-      <c r="B243">
-        <v>1</v>
-      </c>
-      <c r="C243" t="inlineStr">
+      <c r="B253">
+        <v>1</v>
+      </c>
+      <c r="C253" t="inlineStr">
         <is>
           <t>RER</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
+      <c r="D253" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr">
+      <c r="F253" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr">
+      <c r="G253" t="inlineStr">
         <is>
           <t xml:space="preserve">battery module, home storage, Li-ion, NMC811, 19.5 kWh</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr">
+      <c r="I253" t="inlineStr">
         <is>
           <t xml:space="preserve">battery module, home storage, Li-ion, NMC811, 19.5 kWh</t>
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
+    <row r="254">
+      <c r="A254" t="inlineStr">
         <is>
           <t>battery module system production</t>
         </is>
       </c>
-      <c r="B244">
+      <c r="B254">
         <v>6.3504000000000005</v>
       </c>
-      <c r="C244" t="inlineStr">
+      <c r="C254" t="inlineStr">
         <is>
           <t>RER</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
+      <c r="D254" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr">
+      <c r="F254" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr">
+      <c r="G254" t="inlineStr">
         <is>
           <t>battery module system for home storage system module</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr">
+      <c r="I254" t="inlineStr">
         <is>
           <t>battery module system for home storage system module</t>
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
+    <row r="255">
+      <c r="A255" t="inlineStr">
         <is>
           <t xml:space="preserve">battery cell production, Li-ion, NMC811, silicon-graphite anode</t>
         </is>
       </c>
-      <c r="B245">
+      <c r="B255">
         <v>78.34821428571428</v>
       </c>
-      <c r="C245" t="inlineStr">
+      <c r="C255" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
+      <c r="D255" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F245" t="inlineStr">
+      <c r="F255" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr">
+      <c r="G255" t="inlineStr">
         <is>
           <t xml:space="preserve">battery cell, Li-ion, NMC811, silicon-graphite anode</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr">
+      <c r="I255" t="inlineStr">
         <is>
           <t xml:space="preserve">battery cell, Li-ion, NMC811, silicon-graphite anode</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
+    <row r="256">
+      <c r="A256" t="inlineStr">
         <is>
           <t>market for metal working, average for steel product manufacturing</t>
         </is>
       </c>
-      <c r="B246">
+      <c r="B256">
         <v>54.83520000000001</v>
       </c>
-      <c r="C246" t="inlineStr">
+      <c r="C256" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
+      <c r="D256" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr">
+      <c r="F256" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
+      <c r="G256" t="inlineStr">
         <is>
           <t>metal working, average for steel product manufacturing</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr">
+      <c r="I256" t="inlineStr">
         <is>
           <t>metal working, average for steel product manufacturing</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
+    <row r="257">
+      <c r="A257" t="inlineStr">
         <is>
           <t>market for steel, low-alloyed</t>
         </is>
       </c>
-      <c r="B247">
+      <c r="B257">
         <v>54.83520000000001</v>
       </c>
-      <c r="C247" t="inlineStr">
+      <c r="C257" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
+      <c r="D257" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F247" t="inlineStr">
+      <c r="F257" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr">
+      <c r="G257" t="inlineStr">
         <is>
           <t>steel, low-alloyed</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr">
+      <c r="I257" t="inlineStr">
         <is>
           <t>steel, low-alloyed</t>
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
+    <row r="258">
+      <c r="A258" t="inlineStr">
         <is>
           <t>market for transport, freight train</t>
         </is>
       </c>
-      <c r="B248">
+      <c r="B258">
         <v>139.53381428571427</v>
       </c>
-      <c r="C248" t="inlineStr">
+      <c r="C258" t="inlineStr">
         <is>
           <t>Europe without Switzerland</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr">
+      <c r="D258" t="inlineStr">
         <is>
           <t>ton kilometer</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr">
+      <c r="F258" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr">
+      <c r="G258" t="inlineStr">
         <is>
           <t>transport, freight train</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr">
+      <c r="I258" t="inlineStr">
         <is>
           <t>transport, freight train</t>
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
+    <row r="259">
+      <c r="A259" t="inlineStr">
         <is>
           <t>market for transport, freight, lorry 16-32 metric ton, EURO5</t>
         </is>
       </c>
-      <c r="B249">
+      <c r="B259">
         <v>139.53381428571427</v>
       </c>
-      <c r="C249" t="inlineStr">
+      <c r="C259" t="inlineStr">
         <is>
           <t>RER</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
+      <c r="D259" t="inlineStr">
         <is>
           <t>ton kilometer</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr">
+      <c r="F259" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr">
+      <c r="G259" t="inlineStr">
         <is>
           <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr">
+      <c r="I259" t="inlineStr">
         <is>
           <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
+    <row r="260">
+      <c r="A260" t="inlineStr">
         <is>
           <t>market for transport, freight, sea, container ship</t>
         </is>
       </c>
-      <c r="B250">
+      <c r="B260">
         <v>1116.2705142857142</v>
       </c>
-      <c r="C250" t="inlineStr">
+      <c r="C260" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr">
+      <c r="D260" t="inlineStr">
         <is>
           <t>ton kilometer</t>
         </is>
       </c>
-      <c r="F250" t="inlineStr">
+      <c r="F260" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr">
+      <c r="G260" t="inlineStr">
         <is>
           <t>transport, freight, sea, container ship</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr">
+      <c r="I260" t="inlineStr">
         <is>
           <t>transport, freight, sea, container ship</t>
         </is>

--- a/premise/data/additional_inventories/lci-home-batteries.xlsx
+++ b/premise/data/additional_inventories/lci-home-batteries.xlsx
@@ -913,7 +913,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L260"/>
+  <dimension ref="A1:L262"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.5" customWidth="1"/>
@@ -1766,7 +1766,7 @@
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery module production, home storage, Li-ion, LFP, 14.4 kWh</t>
+          <t xml:space="preserve">battery module production, home storage, lithium-ion, lfp, 14.4 kwh</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2271,7 +2271,7 @@
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery module production, home storage, Li-ion, NMC811, 19.5 kWh</t>
+          <t xml:space="preserve">battery module production, home storage, lithium-ion, nmc811, 19.5 kwh</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery module production, home storage, Li-ion, LFP, 14.4 kWh</t>
+          <t xml:space="preserve">battery module production, home storage, lithium-ion, lfp, 14.4 kwh</t>
         </is>
       </c>
     </row>
@@ -4946,69 +4946,36 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Exchanges</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>product</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery module production, home storage, Li-ion, LFP, 14.4 kWh</t>
-        </is>
-      </c>
-      <c r="B234">
-        <v>1</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -5016,30 +4983,40 @@
           <t>unit</t>
         </is>
       </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery module, home storage, Li-ion, LFP, 14.4 kWh</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery module, home storage, Li-ion, LFP, 14.4 kWh</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>battery module system production</t>
+          <t xml:space="preserve">battery module production, home storage, lithium-ion, lfp, 14.4 kwh</t>
         </is>
       </c>
       <c r="B235">
-        <v>6.3504000000000005</v>
+        <v>1</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -5048,37 +5025,37 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>battery module system for home storage system module</t>
+          <t xml:space="preserve">battery module, home storage, Li-ion, LFP, 14.4 kWh</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>battery module system for home storage system module</t>
+          <t xml:space="preserve">battery module, home storage, Li-ion, LFP, 14.4 kWh</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>market for battery cell, Li-ion, LFP</t>
+          <t>battery module system production</t>
         </is>
       </c>
       <c r="B236">
-        <v>90.0</v>
+        <v>6.3504000000000005</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -5093,23 +5070,23 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>battery cell, Li-ion, LFP</t>
+          <t>battery module system for home storage system module</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>battery cell, Li-ion, LFP</t>
+          <t>battery module system for home storage system module</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>market for metal working, average for steel product manufacturing</t>
+          <t>market for battery cell, Li-ion, LFP</t>
         </is>
       </c>
       <c r="B237">
-        <v>54.83520000000001</v>
+        <v>90.0</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -5128,19 +5105,19 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>metal working, average for steel product manufacturing</t>
+          <t>battery cell, Li-ion, LFP</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>metal working, average for steel product manufacturing</t>
+          <t>battery cell, Li-ion, LFP</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>market for steel, low-alloyed</t>
+          <t>market for metal working, average for steel product manufacturing</t>
         </is>
       </c>
       <c r="B238">
@@ -5163,32 +5140,32 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t>metal working, average for steel product manufacturing</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t>metal working, average for steel product manufacturing</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>market for transport, freight train</t>
+          <t>market for steel, low-alloyed</t>
         </is>
       </c>
       <c r="B239">
-        <v>151.1856</v>
+        <v>54.83520000000001</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Europe without Switzerland</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>ton kilometer</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -5198,19 +5175,19 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>transport, freight train</t>
+          <t>steel, low-alloyed</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>transport, freight train</t>
+          <t>steel, low-alloyed</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>market for transport, freight, lorry 16-32 metric ton, EURO5</t>
+          <t>market for transport, freight train</t>
         </is>
       </c>
       <c r="B240">
@@ -5218,7 +5195,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>Europe without Switzerland</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -5233,127 +5210,162 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
+          <t>transport, freight train</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
+          <t>transport, freight train</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
+          <t>market for transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+      <c r="B241">
+        <v>151.1856</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
           <t>market for transport, freight, sea, container ship</t>
         </is>
       </c>
-      <c r="B241">
+      <c r="B242">
         <v>1209.4848</v>
       </c>
-      <c r="C241" t="inlineStr">
+      <c r="C242" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
+      <c r="D242" t="inlineStr">
         <is>
           <t>ton kilometer</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr">
+      <c r="F242" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr">
+      <c r="G242" t="inlineStr">
         <is>
           <t>transport, freight, sea, container ship</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr">
+      <c r="I242" t="inlineStr">
         <is>
           <t>transport, freight, sea, container ship</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery module production, home storage, Li-ion, NMC811, 19.5 kWh</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t xml:space="preserve">battery module production, home storage, lithium-ion, nmc811, 19.5 kwh</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B246">
-        <v>1</v>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery module, home storage, Li-ion, NMC811, 19.5 kWh</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B247">
+        <v>1</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>reference product</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">battery module, home storage, Li-ion, NMC811, 19.5 kWh</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells.</t>
+          <t>unit</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Jasper etal2022 DOI10.1016/j.jclepro.2022.132899,public author PDF https://publikationen.bibliothek.kit.edu/1000148250/149191979 . Existing accepted LFP160Wh/kg andNMC811280Wh/kg cell references in chemistry-specific capacity markets; this is an explicit adapted engineering variant,not reproduction of the measured source140/190Wh/kg pouch cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
+      <c r="B251" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: cell modules, home 19.5kWh NMC811, capacity-consistent reference. Former reference product: cell modules, home 19.5kWh NMC811, capacity-consistent reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED HOME-STORAGE COMPONENT LIFE BUDGETS, issue67,2026-10-18. Jasper etal2022 DOI10.1016/j.jclepro.2022.132899 Table3,minimum/maximum calendar and cyclelife. Recompute for retained13years/2500cycles,NOT copy published20year/7300cycle factors. For eachcomponent selecthigh/lowmanufacturedsets=max(1,systemyears/componentyears,systemcycles/componentcycles),usingpairedlow/highlife endpoints,then midpointsets as engineeringexpectedlifetimeattribution. Clampatonebecauseanewcompleteinstalledsetisrequired; no assumedreusecredit for residualcomponentlife. This is not a probabilisticfailure distribution or literal fractionalinstallation. ReferenceLFPcellsets1,NMC811cellsets1.125;charger/inverter/controls/moduleBMSsets1.3125;cables1.15;housing/module steel1.0. Sourcepublished1.96/2.43cell and1.92electronics factors refer20years/7300cycles andmustnot be blindly transferred. Each home system activity now means an installeddesignplusits13yearmanufacturingreplacementbudget; labelsnominalkWhstayinstalledcapacity,not manufacturedcapacitysum. Multiplycellmanufactureonly bycellfactor within newunitmodule; moduleBMS follows electronicsfactor,modulesteel/rolling remainoneinstalledset. Externalsteelhousingremainsone,externalcontroller/electronics,charger,inverter andcablesfollowtheir own factors. Do not multiplythewholemodule anditscellsagain or buyanotherfullhome systemfor inverterfailure. Increasecomponentfreight withactualmanufacturedcomponentmass; retaininitialassemblyelectricityonce because source replacementassemblyenergy is unspecified,which remains a coveragegap. Existing servicewrapperstays1/consumerlifetimekWh fromissue66; operatingelectricity,DoD,nominalinstalledcapacity andcalendarhorizonunchanged. Transportation is at original routeintensities; packaging/maintenance labour and returntransport are gaps. Device-specific treatment/recycling is not invented; no recoverycredits orprimarysecondaryshares added. Future electronicsdurability is a sourceassumption,not verifiedmodernfleetlife. Sensitivityuseslistedmin/maxsets andsourcecalendar/cyclelimits. Numericreference:{"LFP":{"min_sets":1,"max_sets":1,"reference_sets":1.0},"NMC811":{"min_sets":1,"max_sets":1.25,"reference_sets":1.125},"electronics":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"inverter":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"charger":{"min_sets":1,"max_sets":1.625,"reference_sets":1.3125},"cable":{"min_sets":1,"max_sets":1.3,"reference_sets":1.15},"housing":{"min_sets":1,"max_sets":1,"reference_sets":1.0}}
@@ -5362,177 +5374,119 @@
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>name</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>product</t>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery module production, home storage, Li-ion, NMC811, 19.5 kWh</t>
-        </is>
-      </c>
-      <c r="B253">
-        <v>1</v>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery module, home storage, Li-ion, NMC811, 19.5 kWh</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery module, home storage, Li-ion, NMC811, 19.5 kWh</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>battery module system production</t>
-        </is>
-      </c>
-      <c r="B254">
-        <v>6.3504000000000005</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>battery module system for home storage system module</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>battery module system for home storage system module</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery cell production, Li-ion, NMC811, silicon-graphite anode</t>
+          <t xml:space="preserve">battery module production, home storage, lithium-ion, nmc811, 19.5 kwh</t>
         </is>
       </c>
       <c r="B255">
-        <v>78.34821428571428</v>
+        <v>1</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery cell, Li-ion, NMC811, silicon-graphite anode</t>
+          <t xml:space="preserve">battery module, home storage, Li-ion, NMC811, 19.5 kWh</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery cell, Li-ion, NMC811, silicon-graphite anode</t>
+          <t xml:space="preserve">battery module, home storage, Li-ion, NMC811, 19.5 kWh</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>market for metal working, average for steel product manufacturing</t>
+          <t>battery module system production</t>
         </is>
       </c>
       <c r="B256">
-        <v>54.83520000000001</v>
+        <v>6.3504000000000005</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -5547,23 +5501,23 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>metal working, average for steel product manufacturing</t>
+          <t>battery module system for home storage system module</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>metal working, average for steel product manufacturing</t>
+          <t>battery module system for home storage system module</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>market for steel, low-alloyed</t>
+          <t xml:space="preserve">battery cell production, lithium-ion, nmc811, silicon-graphite anode</t>
         </is>
       </c>
       <c r="B257">
-        <v>54.83520000000001</v>
+        <v>78.34821428571428</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -5582,32 +5536,32 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC811, silicon-graphite anode</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC811, silicon-graphite anode</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>market for transport, freight train</t>
+          <t>market for metal working, average for steel product manufacturing</t>
         </is>
       </c>
       <c r="B258">
-        <v>139.53381428571427</v>
+        <v>54.83520000000001</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Europe without Switzerland</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>ton kilometer</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -5617,32 +5571,32 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>transport, freight train</t>
+          <t>metal working, average for steel product manufacturing</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>transport, freight train</t>
+          <t>metal working, average for steel product manufacturing</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>market for transport, freight, lorry 16-32 metric ton, EURO5</t>
+          <t>market for steel, low-alloyed</t>
         </is>
       </c>
       <c r="B259">
-        <v>139.53381428571427</v>
+        <v>54.83520000000001</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>ton kilometer</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -5652,45 +5606,115 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
+          <t>steel, low-alloyed</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
+          <t>steel, low-alloyed</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
+          <t>market for transport, freight train</t>
+        </is>
+      </c>
+      <c r="B260">
+        <v>139.53381428571427</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>market for transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+      <c r="B261">
+        <v>139.53381428571427</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
           <t>market for transport, freight, sea, container ship</t>
         </is>
       </c>
-      <c r="B260">
+      <c r="B262">
         <v>1116.2705142857142</v>
       </c>
-      <c r="C260" t="inlineStr">
+      <c r="C262" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
+      <c r="D262" t="inlineStr">
         <is>
           <t>ton kilometer</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr">
+      <c r="F262" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr">
+      <c r="G262" t="inlineStr">
         <is>
           <t>transport, freight, sea, container ship</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr">
+      <c r="I262" t="inlineStr">
         <is>
           <t>transport, freight, sea, container ship</t>
         </is>
